--- a/optionalfiles/turn_table_into_list.xlsx
+++ b/optionalfiles/turn_table_into_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paul/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9A3E96A4-C353-D24F-BE38-1BCD6746C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8340CEBC-3130-CE43-8B27-CA336D727040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2000" yWindow="2500" windowWidth="22820" windowHeight="14160" xr2:uid="{482A10C3-D080-6E48-B009-BFDD137CBF74}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="372">
   <si>
     <t>city</t>
   </si>
@@ -1148,13 +1148,7 @@
     <t>MAKE LIST</t>
   </si>
   <si>
-    <t>ADD [</t>
-  </si>
-  <si>
-    <t>REMOVE COMMA AT END</t>
-  </si>
-  <si>
-    <t>ADD ]</t>
+    <t>ADD [ ]</t>
   </si>
 </sst>
 </file>
@@ -2140,8 +2134,8 @@
         <v>371</v>
       </c>
       <c r="L3" s="1" t="str">
-        <f>"["&amp;L2</f>
-        <v>[{'lat': np.float64(51.5072), 'long': np.float64(-0.1275), 'officialname': 'London'}, {'lat': np.float64(52.48), 'long': np.float64(-1.9025), 'officialname': 'Birmingham'}, {'lat': np.float64(50.8058), 'long': np.float64(-1.0872), 'officialname': 'Portsmouth'}, {'lat': np.float64(50.9025), 'long': np.float64(-1.4042), 'officialname': 'Southampton'}, {'lat': np.float64(52.9561), 'long': np.float64(-1.1512), 'officialname': 'Nottingham'}, {'lat': np.float64(51.4536), 'long': np.float64(-2.5975), 'officialname': 'Bristol'}, {'lat': np.float64(53.479), 'long': np.float64(-2.2452), 'officialname': 'Manchester'}, {'lat': np.float64(53.4094), 'long': np.float64(-2.9785), 'officialname': 'Liverpool'}, {'lat': np.float64(52.6344), 'long': np.float64(-1.1319), 'officialname': 'Leicester'}, {'lat': np.float64(50.8147), 'long': np.float64(-0.3714), 'officialname': 'Worthing'}, {'lat': np.float64(52.4081), 'long': np.float64(-1.5106), 'officialname': 'Coventry'}, {'lat': np.float64(54.5964), 'long': np.float64(-5.93), 'officialname': 'Belfast'}, {'lat': np.float64(53.8), 'long': np.float64(-1.75), 'officialname': 'Bradford'}, {'lat': np.float64(52.9247), 'long': np.float64(-1.478), 'officialname': 'Derby'}, {'lat': np.float64(50.3714), 'long': np.float64(-4.1422), 'officialname': 'Plymouth'}, {'lat': np.float64(51.4947), 'long': np.float64(-0.1353), 'officialname': 'Westminster'}, {'lat': np.float64(52.5833), 'long': np.float64(-2.1333), 'officialname': 'Wolverhampton'}, {'lat': np.float64(52.2304), 'long': np.float64(-0.8938), 'officialname': 'Northampton'}, {'lat': np.float64(52.6286), 'long': np.float64(1.2928), 'officialname': 'Norwich'}, {'lat': np.float64(51.8783), 'long': np.float64(-0.4147), 'officialname': 'Luton'}, {'lat': np.float64(52.413), 'long': np.float64(-1.778), 'officialname': 'Solihull'}, {'lat': np.float64(51.544), 'long': np.float64(-0.1027), 'officialname': 'Islington'}, {'lat': np.float64(57.15), 'long': np.float64(-2.11), 'officialname': 'Aberdeen'}, {'lat': np.float64(51.3727), 'long': np.float64(-0.1099), 'officialname': 'Croydon'}, {'lat': np.float64(50.72), 'long': np.float64(-1.88), 'officialname': 'Bournemouth'}, {'lat': np.float64(51.58), 'long': np.float64(0.49), 'officialname': 'Basildon'}, {'lat': np.float64(51.272), 'long': np.float64(0.529), 'officialname': 'Maidstone'}, {'lat': np.float64(51.5575), 'long': np.float64(0.0858), 'officialname': 'Ilford'}, {'lat': np.float64(53.39), 'long': np.float64(-2.59), 'officialname': 'Warrington'}, {'lat': np.float64(51.75), 'long': np.float64(-1.25), 'officialname': 'Oxford'}, {'lat': np.float64(51.5836), 'long': np.float64(-0.3464), 'officialname': 'Harrow'}, {'lat': np.float64(52.519), 'long': np.float64(-1.995), 'officialname': 'West Bromwich'}, {'lat': np.float64(51.8667), 'long': np.float64(-2.25), 'officialname': 'Gloucester'}, {'lat': np.float64(53.96), 'long': np.float64(-1.08), 'officialname': 'York'}, {'lat': np.float64(53.8142), 'long': np.float64(-3.0503), 'officialname': 'Blackpool'}, {'lat': np.float64(53.4083), 'long': np.float64(-2.1494), 'officialname': 'Stockport'}, {'lat': np.float64(53.424), 'long': np.float64(-2.322), 'officialname': 'Sale'}, {'lat': np.float64(51.5975), 'long': np.float64(-0.0681), 'officialname': 'Tottenham'}, {'lat': np.float64(52.2053), 'long': np.float64(0.1192), 'officialname': 'Cambridge'}, {'lat': np.float64(51.5768), 'long': np.float64(0.1801), 'officialname': 'Romford'}, {'lat': np.float64(51.8917), 'long': np.float64(0.903), 'officialname': 'Colchester'}, {'lat': np.float64(51.6287), 'long': np.float64(-0.7482), 'officialname': 'High Wycombe'}, {'lat': np.float64(54.9556), 'long': np.float64(-1.6), 'officialname': 'Gateshead'}, {'lat': np.float64(51.5084), 'long': np.float64(-0.5881), 'officialname': 'Slough'}, {'lat': np.float64(53.748), 'long': np.float64(-2.482), 'officialname': 'Blackburn'}, {'lat': np.float64(51.73), 'long': np.float64(0.48), 'officialname': 'Chelmsford'}, {'lat': np.float64(53.61), 'long': np.float64(-2.16), 'officialname': 'Rochdale'}, {'lat': np.float64(53.43), 'long': np.float64(-1.357), 'officialname': 'Rotherham'}, {'lat': np.float64(51.584), 'long': np.float64(-0.021), 'officialname': 'Walthamstow'}, {'lat': np.float64(51.2667), 'long': np.float64(-1.0876), 'officialname': 'Basingstoke'}, {'lat': np.float64(53.483), 'long': np.float64(-2.2931), 'officialname': 'Salford'}, {'lat': np.float64(51.4668), 'long': np.float64(-0.375), 'officialname': 'Hounslow'}, {'lat': np.float64(51.5528), 'long': np.float64(-0.2979), 'officialname': 'Wembley'}, {'lat': np.float64(52.1911), 'long': np.float64(-2.2206), 'officialname': 'Worcester'}, {'lat': np.float64(51.4928), 'long': np.float64(-0.2229), 'officialname': 'Hammersmith'}, {'lat': np.float64(51.5864), 'long': np.float64(0.6049), 'officialname': 'Rayleigh'}, {'lat': np.float64(51.7526), 'long': np.float64(-0.4692), 'officialname': 'Hemel Hempstead'}, {'lat': np.float64(51.38), 'long': np.float64(-2.36), 'officialname': 'Bath'}, {'lat': np.float64(51.5127), 'long': np.float64(-0.4211), 'officialname': 'Hayes'}, {'lat': np.float64(54.527), 'long': np.float64(-1.5526), 'officialname': 'Darlington'}, {'lat': np.float64(50.8352), 'long': np.float64(-0.1758), 'officialname': 'Hove'}, {'lat': np.float64(50.85), 'long': np.float64(0.57), 'officialname': 'Hastings'}, {'lat': np.float64(51.655), 'long': np.float64(-0.3957), 'officialname': 'Watford'}, {'lat': np.float64(51.9017), 'long': np.float64(-0.2019), 'officialname': 'Stevenage'}, {'lat': np.float64(54.69), 'long': np.float64(-1.21), 'officialname': 'Hartlepool'}, {'lat': np.float64(53.19), 'long': np.float64(-2.89), 'officialname': 'Chester'}, {'lat': np.float64(51.4828), 'long': np.float64(-0.195), 'officialname': 'Fulham'}, {'lat': np.float64(52.523), 'long': np.float64(-1.468), 'officialname': 'Nuneaton'}, {'lat': np.float64(51.5175), 'long': np.float64(-0.2988), 'officialname': 'Ealing'}, {'lat': np.float64(51.8168), 'long': np.float64(-0.8124), 'officialname': 'Aylesbury'}, {'lat': np.float64(51.6154), 'long': np.float64(-0.0708), 'officialname': 'Edmonton'}, {'lat': np.float64(51.755), 'long': np.float64(-0.336), 'officialname': 'Saint Albans'}, {'lat': np.float64(53.789), 'long': np.float64(-2.248), 'officialname': 'Burnley'}, {'lat': np.float64(53.7167), 'long': np.float64(-1.6356), 'officialname': 'Batley'}, {'lat': np.float64(53.5809), 'long': np.float64(-0.6502), 'officialname': 'Scunthorpe'}, {'lat': np.float64(52.508), 'long': np.float64(-2.089), 'officialname': 'Dudley'}, {'lat': np.float64(51.4575), 'long': np.float64(-0.1175), 'officialname': 'Brixton'}, {'lat': np.float64(51.5111), 'long': np.float64(-0.3756), 'officialname': 'Southall'}, {'lat': np.float64(55.8456), 'long': np.float64(-4.4239), 'officialname': 'Paisley'}, {'lat': np.float64(51.37), 'long': np.float64(0.52), 'officialname': 'Chatham'}, {'lat': np.float64(51.5323), 'long': np.float64(0.0554), 'officialname': 'East Ham'}, {'lat': np.float64(51.346), 'long': np.float64(-2.977), 'officialname': 'Weston-super-Mare'}, {'lat': np.float64(54.8947), 'long': np.float64(-2.9364), 'officialname': 'Carlisle'}, {'lat': np.float64(54.995), 'long': np.float64(-1.43), 'officialname': 'South Shields'}, {'lat': np.float64(55.7644), 'long': np.float64(-4.1769), 'officialname': 'East Kilbride'}, {'lat': np.float64(52.8019), 'long': np.float64(-1.6367), 'officialname': 'Burton upon Trent'}, {'lat': np.float64(53.9919), 'long': np.float64(-1.5378), 'officialname': 'Harrogate'}, {'lat': np.float64(53.099), 'long': np.float64(-2.44), 'officialname': 'Crewe'}, {'lat': np.float64(52.48), 'long': np.float64(1.75), 'officialname': 'Lowestoft'}, {'lat': np.float64(52.37), 'long': np.float64(-1.26), 'officialname': 'Rugby'}, {'lat': np.float64(51.623), 'long': np.float64(0.009), 'officialname': 'Chingford'}, {'lat': np.float64(51.5404), 'long': np.float64(-0.4778), 'officialname': 'Uxbridge'}, {'lat': np.float64(52.58), 'long': np.float64(-1.98), 'officialname': 'Walsall'}, {'lat': np.float64(51.475), 'long': np.float64(0.33), 'officialname': 'Grays'}, {'lat': np.float64(51.3868), 'long': np.float64(-0.4133), 'officialname': 'Walton upon Thames'}, {'lat': np.float64(51.4002), 'long': np.float64(-0.1086), 'officialname': 'Thornton Heath'}, {'lat': np.float64(51.599), 'long': np.float64(-0.187), 'officialname': 'Finchley'}, {'lat': np.float64(51.5), 'long': np.float64(-0.19), 'officialname': 'Kensington'}, {'lat': np.float64(52.974), 'long': np.float64(-0.0214), 'officialname': 'Boston'}, {'lat': np.float64(50.4353), 'long': np.float64(-3.5625), 'officialname': 'Paignton'}, {'lat': np.float64(50.88), 'long': np.float64(-1.03), 'officialname': 'Waterlooville'}, {'lat': np.float64(53.875), 'long': np.float64(-1.706), 'officialname': 'Guiseley'}, {'lat': np.float64(51.5565), 'long': np.float64(0.2128), 'officialname': 'Hornchurch'}, {'lat': np.float64(51.4009), 'long': np.float64(-0.1517), 'officialname': 'Mitcham'}, {'lat': np.float64(51.4496), 'long': np.float64(-0.4089), 'officialname': 'Feltham'}, {'lat': np.float64(52.4575), 'long': np.float64(-2.1479), 'officialname': 'Stourbridge'}, {'lat': np.float64(51.375), 'long': np.float64(0.5), 'officialname': 'Rochester'}, {'lat': np.float64(53.691), 'long': np.float64(-1.633), 'officialname': 'Dewsbury'}, {'lat': np.float64(51.5135), 'long': np.float64(-0.2707), 'officialname': 'Acton'}, {'lat': np.float64(51.449), 'long': np.float64(-0.337), 'officialname': 'Twickenham'}, {'lat': np.float64(53.046), 'long': np.float64(-2.993), 'officialname': 'Wrecsam'}, {'lat': np.float64(53.279), 'long': np.float64(-2.897), 'officialname': 'Ellesmere Port'}, {'lat': np.float64(54.66), 'long': np.float64(-5.67), 'officialname': 'Bangor'}, {'lat': np.float64(51.019), 'long': np.float64(-3.1), 'officialname': 'Taunton'}, {'lat': np.float64(52.7725), 'long': np.float64(-1.2078), 'officialname': 'Loughborough'}, {'lat': np.float64(51.54), 'long': np.float64(0.08), 'officialname': 'Barking'}, {'lat': np.float64(51.6185), 'long': np.float64(-0.2729), 'officialname': 'Edgware'}, {'lat': np.float64(50.8094), 'long': np.float64(-0.5409), 'officialname': 'Littlehampton'}, {'lat': np.float64(51.576), 'long': np.float64(-0.433), 'officialname': 'Ruislip'}, {'lat': np.float64(51.4279), 'long': np.float64(-0.1235), 'officialname': 'Streatham'}, {'lat': np.float64(51.132), 'long': np.float64(0.263), 'officialname': 'Royal Tunbridge Wells'}, {'lat': np.float64(53.35), 'long': np.float64(-3.003), 'officialname': 'Bebington'}, {'lat': np.float64(53.25), 'long': np.float64(-2.13), 'officialname': 'Macclesfield'}, {'lat': np.float64(52.3028), 'long': np.float64(-0.6944), 'officialname': 'Wellingborough'}, {'lat': np.float64(52.3931), 'long': np.float64(-0.7229), 'officialname': 'Kettering'}, {'lat': np.float64(51.878), 'long': np.float64(0.55), 'officialname': 'Braintree'}, {'lat': np.float64(52.2919), 'long': np.float64(-1.5358), 'officialname': 'Royal Leamington Spa'}, {'lat': np.float64(54.1108), 'long': np.float64(-3.2261), 'officialname': 'Barrow in Furness'}, {'lat': np.float64(56.0719), 'long': np.float64(-3.4393), 'officialname': 'Dunfermline'}, {'lat': np.float64(53.3838), 'long': np.float64(-2.3547), 'officialname': 'Altrincham'}, {'lat': np.float64(54.0489), 'long': np.float64(-2.8014), 'officialname': 'Lancaster'}, {'lat': np.float64(53.4872), 'long': np.float64(-3.0343), 'officialname': 'Crosby'}, {'lat': np.float64(53.4457), 'long': np.float64(-2.9891), 'officialname': 'Bootle'}, {'lat': np.float64(51.5423), 'long': np.float64(-0.0026), 'officialname': 'Stratford'}, {'lat': np.float64(51.0792), 'long': np.float64(1.1794), 'officialname': 'Folkestone'}, {'lat': np.float64(55.945), 'long': np.float64(-3.994), 'officialname': 'Cumbernauld'}, {'lat': np.float64(51.208), 'long': np.float64(-1.48), 'officialname': 'Andover'}, {'lat': np.float64(51.66), 'long': np.float64(-3.81), 'officialname': 'Neath'}, {'lat': np.float64(52.488), 'long': np.float64(-2.05), 'officialname': 'Rowley Regis'}, {'lat': np.float64(54.2825), 'long': np.float64(-0.4), 'officialname': 'Scarborough'}, {'lat': np.float64(55.98), 'long': np.float64(-3.17), 'officialname': 'Leith'}, {'lat': np.float64(50.9452), 'long': np.float64(-2.637), 'officialname': 'Yeovil'}, {'lat': np.float64(51.451), 'long': np.float64(0.052), 'officialname': 'Eltham'}, {'lat': np.float64(51.5541), 'long': np.float64(-0.1744), 'officialname': 'Hampstead'}, {'lat': np.float64(53.125), 'long': np.float64(-1.261), 'officialname': 'Sutton in Ashfield'}, {'lat': np.float64(51.4015), 'long': np.float64(-0.1949), 'officialname': 'Morden'}, {'lat': np.float64(51.6444), 'long': np.float64(-0.1997), 'officialname': 'Barnet'}, {'lat': np.float64(53.4466), 'long': np.float64(-2.3086), 'officialname': 'Stretford'}, {'lat': np.float64(51.408), 'long': np.float64(-0.022), 'officialname': 'Beckenham'}, {'lat': np.float64(51.5299), 'long': np.float64(-0.3488), 'officialname': 'Greenford'}, {'lat': np.float64(51.702), 'long': np.float64(-0.035), 'officialname': 'Cheshunt'}, {'lat': np.float64(53.48), 'long': np.float64(-2.89), 'officialname': 'Kirkby'}, {'lat': np.float64(51.07), 'long': np.float64(-1.79), 'officialname': 'Salisbury'}, {'lat': np.float64(53.4897), 'long': np.float64(-2.0952), 'officialname': 'Ashton'}, {'lat': np.float64(51.394), 'long': np.float64(-0.307), 'officialname': 'Surbiton'}, {'lat': np.float64(53.716), 'long': np.float64(-1.356), 'officialname': 'Castleford'}, {'lat': np.float64(51.4452), 'long': np.float64(-0.0207), 'officialname': 'Catford'}, {'lat': np.float64(53.3042), 'long': np.float64(-1.1244), 'officialname': 'Worksop'}, {'lat': np.float64(53.7492), 'long': np.float64(-1.6023), 'officialname': 'Morley'}, {'lat': np.float64(51.743), 'long': np.float64(-3.378), 'officialname': 'Merthyr Tudful'}, {'lat': np.float64(53.555), 'long': np.float64(-2.187), 'officialname': 'Middleton'}, {'lat': np.float64(51.2834), 'long': np.float64(-0.8456), 'officialname': 'Fleet'}, {'lat': np.float64(50.85), 'long': np.float64(-1.18), 'officialname': 'Fareham'}, {'lat': np.float64(53.4487), 'long': np.float64(-2.3747), 'officialname': 'Urmston'}, {'lat': np.float64(51.3656), 'long': np.float64(-0.1963), 'officialname': 'Sutton'}, {'lat': np.float64(51.578), 'long': np.float64(-3.218), 'officialname': 'Caerphilly'}, {'lat': np.float64(51.128), 'long': np.float64(-2.993), 'officialname': 'Bridgwater'}, {'lat': np.float64(51.401), 'long': np.float64(-1.323), 'officialname': 'Newbury'}, {'lat': np.float64(51.4594), 'long': np.float64(0.1097), 'officialname': 'Welling'}, {'lat': np.float64(51.46), 'long': np.float64(-2.505), 'officialname': 'Kingswood'}, {'lat': np.float64(51.886), 'long': np.float64(-0.521), 'officialname': 'Dunstable'}, {'lat': np.float64(51.336), 'long': np.float64(1.416), 'officialname': 'Ramsgate'}, {'lat': np.float64(51.393), 'long': np.float64(0.478), 'officialname': 'Strood'}, {'lat': np.float64(53.5533), 'long': np.float64(-0.0215), 'officialname': 'Cleethorpes'}, {'lat': np.float64(51.5932), 'long': np.float64(-0.3894), 'officialname': 'Pinner'}, {'lat': np.float64(52.606), 'long': np.float64(1.729), 'officialname': 'Great Yarmouth'}, {'lat': np.float64(52.9711), 'long': np.float64(-1.3092), 'officialname': 'Ilkeston'}, {'lat': np.float64(53.653), 'long': np.float64(-2.632), 'officialname': 'Chorley'}, {'lat': np.float64(51.37), 'long': np.float64(1.13), 'officialname': 'Herne Bay'}, {'lat': np.float64(51.872), 'long': np.float64(0.1725), 'officialname': 'Bishops Stortford'}, {'lat': np.float64(53.005), 'long': np.float64(-1.127), 'officialname': 'Arnold'}, {'lat': np.float64(52.724), 'long': np.float64(-1.369), 'officialname': 'Coalville'}, {'lat': np.float64(51.994), 'long': np.float64(-0.732), 'officialname': 'Bletchley'}, {'lat': np.float64(51.9165), 'long': np.float64(-0.6617), 'officialname': 'Leighton Buzzard'}, {'lat': np.float64(55.86), 'long': np.float64(-3.98), 'officialname': 'Airdrie'}, {'lat': np.float64(55.126), 'long': np.float64(-1.514), 'officialname': 'Blyth'}, {'lat': np.float64(51.574), 'long': np.float64(0.4181), 'officialname': 'Laindon'}, {'lat': np.float64(51.684), 'long': np.float64(-4.163), 'officialname': 'Llanelli'}, {'lat': np.float64(52.927), 'long': np.float64(-1.215), 'officialname': 'Beeston'}, {'lat': np.float64(52.4629), 'long': np.float64(-1.8542), 'officialname': 'Small Heath'}, {'lat': np.float64(55.0456), 'long': np.float64(-1.4443), 'officialname': 'Whitley Bay'}, {'lat': np.float64(53.4554), 'long': np.float64(-2.1122), 'officialname': 'Denton'}, {'lat': np.float64(52.932), 'long': np.float64(-1.127), 'officialname': 'West Bridgford'}, {'lat': np.float64(51.6578), 'long': np.float64(-0.2722), 'officialname': 'Borehamwood'}, {'lat': np.float64(56.0011), 'long': np.float64(-3.7835), 'officialname': 'Falkirk'}, {'lat': np.float64(53.5239), 'long': np.float64(-2.3991), 'officialname': 'Walkden'}, {'lat': np.float64(51.5878), 'long': np.float64(-0.3086), 'officialname': 'Kenton'}, {'lat': np.float64(54.0819), 'long': np.float64(-0.1923), 'officialname': 'Bridlington'}, {'lat': np.float64(54.61), 'long': np.float64(-1.27), 'officialname': 'Billingham'}, {'lat': np.float64(52.918), 'long': np.float64(-0.638), 'officialname': 'Grantham'}, {'lat': np.float64(55.0097), 'long': np.float64(-1.4448), 'officialname': 'North Shields'}, {'lat': np.float64(51.947), 'long': np.float64(-0.283), 'officialname': 'Hitchin'}, {'lat': np.float64(52.7858), 'long': np.float64(-0.1529), 'officialname': 'Spalding'}, {'lat': np.float64(51.36), 'long': np.float64(0.61), 'officialname': 'Rainham'}, {'lat': np.float64(51.978), 'long': np.float64(-0.23), 'officialname': 'Letchworth'}, {'lat': np.float64(51.6114), 'long': np.float64(0.5207), 'officialname': 'Wickford'}, {'lat': np.float64(53.4111), 'long': np.float64(-2.8403), 'officialname': 'Huyton'}, {'lat': np.float64(51.6717), 'long': np.float64(-1.2783), 'officialname': 'Abingdon'}, {'lat': np.float64(51.32), 'long': np.float64(-2.208), 'officialname': 'Trowbridge'}, {'lat': np.float64(52.5812), 'long': np.float64(-1.093), 'officialname': 'Wigston Magna'}, {'lat': np.float64(51.606), 'long': np.float64(-1.241), 'officialname': 'Didcot'}, {'lat': np.float64(51.433), 'long': np.float64(-0.933), 'officialname': 'Earley'}, {'lat': np.float64(51.459), 'long': np.float64(0.138), 'officialname': 'Bexleyheath'}, {'lat': np.float64(53.4429), 'long': np.float64(-1.4698), 'officialname': 'Ecclesfield'}, {'lat': np.float64(53.698), 'long': np.float64(-2.461), 'officialname': 'Darwen'}, {'lat': np.float64(53.5333), 'long': np.float64(-2.2833), 'officialname': 'Prestwich'}, {'lat': np.float64(51.602), 'long': np.float64(-3.342), 'officialname': 'Pontypridd'}, {'lat': np.float64(55.828), 'long': np.float64(-4.214), 'officialname': 'Rutherglen'}, {'lat': np.float64(51.1295), 'long': np.float64(1.3089), 'officialname': 'Dover'}, {'lat': np.float64(50.8365), 'long': np.float64(-0.7792), 'officialname': 'Chichester'}, {'lat': np.float64(51.2226), 'long': np.float64(1.4006), 'officialname': 'Deal'}, {'lat': np.float64(51.9), 'long': np.float64(-1.15), 'officialname': 'Bicester'}, {'lat': np.float64(51.5467), 'long': np.float64(-0.37), 'officialname': 'Northolt'}, {'lat': np.float64(55.7742), 'long': np.float64(-3.9183), 'officialname': 'Wishaw'}, {'lat': np.float64(51.3652), 'long': np.float64(-0.1676), 'officialname': 'Carshalton'}, {'lat': np.float64(53.001), 'long': np.float64(-1.197), 'officialname': 'Bulwell'}, {'lat': np.float64(54.591), 'long': np.float64(-5.68), 'officialname': 'Newtownards'}, {'lat': np.float64(54.326), 'long': np.float64(-2.745), 'officialname': 'Kendal'}, {'lat': np.float64(55.082), 'long': np.float64(-1.585), 'officialname': 'Cramlington'}, {'lat': np.float64(52.3353), 'long': np.float64(-2.0579), 'officialname': 'Bromsgrove'}, {'lat': np.float64(51.703), 'long': np.float64(-3.041), 'officialname': 'Pont-y-p≈µl'}, {'lat': np.float64(51.509), 'long': np.float64(-0.338), 'officialname': 'Hanwell'}, {'lat': np.float64(51.2279), 'long': np.float64(-2.3215), 'officialname': 'Frome'}, {'lat': np.float64(51.5981), 'long': np.float64(-0.1149), 'officialname': 'Wood Green'}, {'lat': np.float64(52.5708), 'long': np.float64(-2.0457), 'officialname': 'Darlaston'}, {'lat': np.float64(55.181), 'long': np.float64(-1.568), 'officialname': 'Ashington'}, {'lat': np.float64(52.9877), 'long': np.float64(-2.1327), 'officialname': 'Longton'}, {'lat': np.float64(52.7661), 'long': np.float64(-0.886), 'officialname': 'Melton Mowbray'}, {'lat': np.float64(52.606), 'long': np.float64(-1.9179), 'officialname': 'Aldridge'}, {'lat': np.float64(53.5452), 'long': np.float64(-2.3999), 'officialname': 'Farnworth'}, {'lat': np.float64(51.552), 'long': np.float64(-0.097), 'officialname': 'Highbury'}, {'lat': np.float64(53.3761), 'long': np.float64(-2.1897), 'officialname': 'Cheadle Hulme'}, {'lat': np.float64(54.62), 'long': np.float64(-1.58), 'officialname': 'Newton Aycliffe'}, {'lat': np.float64(52.4299), 'long': np.float64(-1.9355), 'officialname': 'Bournville'}, {'lat': np.float64(52.009), 'long': np.float64(-0.789), 'officialname': 'Shenley Brook End'}, {'lat': np.float64(54.85), 'long': np.float64(-1.83), 'officialname': 'Consett'}, {'lat': np.float64(51.3211), 'long': np.float64(-0.1386), 'officialname': 'Coulsdon'}, {'lat': np.float64(52.566), 'long': np.float64(-2.0728), 'officialname': 'Bilston'}, {'lat': np.float64(52.7001), 'long': np.float64(-2.5157), 'officialname': 'Wellington'}, {'lat': np.float64(54.663), 'long': np.float64(-1.676), 'officialname': 'Bishop Auckland'}, {'lat': np.float64(52.395), 'long': np.float64(-1.979), 'officialname': 'Longbridge'}, {'lat': np.float64(52.614), 'long': np.float64(-2.004), 'officialname': 'Bloxwich'}, {'lat': np.float64(51.5557), 'long': np.float64(0.2512), 'officialname': 'Upminster'}, {'lat': np.float64(53.321), 'long': np.float64(-3.48), 'officialname': 'Rhyl'}, {'lat': np.float64(52.267), 'long': np.float64(-2.153), 'officialname': 'Droitwich'}, {'lat': np.float64(53.5355), 'long': np.float64(-2.5658), 'officialname': 'Hindley'}, {'lat': np.float64(53.549), 'long': np.float64(-2.529), 'officialname': 'Westhoughton'}, {'lat': np.float64(51.3589), 'long': np.float64(1.4394), 'officialname': 'Broadstairs'}</v>
+        <f>"[ "&amp;L2&amp;" ]"</f>
+        <v>[ {'lat': np.float64(51.5072), 'long': np.float64(-0.1275), 'officialname': 'London'}, {'lat': np.float64(52.48), 'long': np.float64(-1.9025), 'officialname': 'Birmingham'}, {'lat': np.float64(50.8058), 'long': np.float64(-1.0872), 'officialname': 'Portsmouth'}, {'lat': np.float64(50.9025), 'long': np.float64(-1.4042), 'officialname': 'Southampton'}, {'lat': np.float64(52.9561), 'long': np.float64(-1.1512), 'officialname': 'Nottingham'}, {'lat': np.float64(51.4536), 'long': np.float64(-2.5975), 'officialname': 'Bristol'}, {'lat': np.float64(53.479), 'long': np.float64(-2.2452), 'officialname': 'Manchester'}, {'lat': np.float64(53.4094), 'long': np.float64(-2.9785), 'officialname': 'Liverpool'}, {'lat': np.float64(52.6344), 'long': np.float64(-1.1319), 'officialname': 'Leicester'}, {'lat': np.float64(50.8147), 'long': np.float64(-0.3714), 'officialname': 'Worthing'}, {'lat': np.float64(52.4081), 'long': np.float64(-1.5106), 'officialname': 'Coventry'}, {'lat': np.float64(54.5964), 'long': np.float64(-5.93), 'officialname': 'Belfast'}, {'lat': np.float64(53.8), 'long': np.float64(-1.75), 'officialname': 'Bradford'}, {'lat': np.float64(52.9247), 'long': np.float64(-1.478), 'officialname': 'Derby'}, {'lat': np.float64(50.3714), 'long': np.float64(-4.1422), 'officialname': 'Plymouth'}, {'lat': np.float64(51.4947), 'long': np.float64(-0.1353), 'officialname': 'Westminster'}, {'lat': np.float64(52.5833), 'long': np.float64(-2.1333), 'officialname': 'Wolverhampton'}, {'lat': np.float64(52.2304), 'long': np.float64(-0.8938), 'officialname': 'Northampton'}, {'lat': np.float64(52.6286), 'long': np.float64(1.2928), 'officialname': 'Norwich'}, {'lat': np.float64(51.8783), 'long': np.float64(-0.4147), 'officialname': 'Luton'}, {'lat': np.float64(52.413), 'long': np.float64(-1.778), 'officialname': 'Solihull'}, {'lat': np.float64(51.544), 'long': np.float64(-0.1027), 'officialname': 'Islington'}, {'lat': np.float64(57.15), 'long': np.float64(-2.11), 'officialname': 'Aberdeen'}, {'lat': np.float64(51.3727), 'long': np.float64(-0.1099), 'officialname': 'Croydon'}, {'lat': np.float64(50.72), 'long': np.float64(-1.88), 'officialname': 'Bournemouth'}, {'lat': np.float64(51.58), 'long': np.float64(0.49), 'officialname': 'Basildon'}, {'lat': np.float64(51.272), 'long': np.float64(0.529), 'officialname': 'Maidstone'}, {'lat': np.float64(51.5575), 'long': np.float64(0.0858), 'officialname': 'Ilford'}, {'lat': np.float64(53.39), 'long': np.float64(-2.59), 'officialname': 'Warrington'}, {'lat': np.float64(51.75), 'long': np.float64(-1.25), 'officialname': 'Oxford'}, {'lat': np.float64(51.5836), 'long': np.float64(-0.3464), 'officialname': 'Harrow'}, {'lat': np.float64(52.519), 'long': np.float64(-1.995), 'officialname': 'West Bromwich'}, {'lat': np.float64(51.8667), 'long': np.float64(-2.25), 'officialname': 'Gloucester'}, {'lat': np.float64(53.96), 'long': np.float64(-1.08), 'officialname': 'York'}, {'lat': np.float64(53.8142), 'long': np.float64(-3.0503), 'officialname': 'Blackpool'}, {'lat': np.float64(53.4083), 'long': np.float64(-2.1494), 'officialname': 'Stockport'}, {'lat': np.float64(53.424), 'long': np.float64(-2.322), 'officialname': 'Sale'}, {'lat': np.float64(51.5975), 'long': np.float64(-0.0681), 'officialname': 'Tottenham'}, {'lat': np.float64(52.2053), 'long': np.float64(0.1192), 'officialname': 'Cambridge'}, {'lat': np.float64(51.5768), 'long': np.float64(0.1801), 'officialname': 'Romford'}, {'lat': np.float64(51.8917), 'long': np.float64(0.903), 'officialname': 'Colchester'}, {'lat': np.float64(51.6287), 'long': np.float64(-0.7482), 'officialname': 'High Wycombe'}, {'lat': np.float64(54.9556), 'long': np.float64(-1.6), 'officialname': 'Gateshead'}, {'lat': np.float64(51.5084), 'long': np.float64(-0.5881), 'officialname': 'Slough'}, {'lat': np.float64(53.748), 'long': np.float64(-2.482), 'officialname': 'Blackburn'}, {'lat': np.float64(51.73), 'long': np.float64(0.48), 'officialname': 'Chelmsford'}, {'lat': np.float64(53.61), 'long': np.float64(-2.16), 'officialname': 'Rochdale'}, {'lat': np.float64(53.43), 'long': np.float64(-1.357), 'officialname': 'Rotherham'}, {'lat': np.float64(51.584), 'long': np.float64(-0.021), 'officialname': 'Walthamstow'}, {'lat': np.float64(51.2667), 'long': np.float64(-1.0876), 'officialname': 'Basingstoke'}, {'lat': np.float64(53.483), 'long': np.float64(-2.2931), 'officialname': 'Salford'}, {'lat': np.float64(51.4668), 'long': np.float64(-0.375), 'officialname': 'Hounslow'}, {'lat': np.float64(51.5528), 'long': np.float64(-0.2979), 'officialname': 'Wembley'}, {'lat': np.float64(52.1911), 'long': np.float64(-2.2206), 'officialname': 'Worcester'}, {'lat': np.float64(51.4928), 'long': np.float64(-0.2229), 'officialname': 'Hammersmith'}, {'lat': np.float64(51.5864), 'long': np.float64(0.6049), 'officialname': 'Rayleigh'}, {'lat': np.float64(51.7526), 'long': np.float64(-0.4692), 'officialname': 'Hemel Hempstead'}, {'lat': np.float64(51.38), 'long': np.float64(-2.36), 'officialname': 'Bath'}, {'lat': np.float64(51.5127), 'long': np.float64(-0.4211), 'officialname': 'Hayes'}, {'lat': np.float64(54.527), 'long': np.float64(-1.5526), 'officialname': 'Darlington'}, {'lat': np.float64(50.8352), 'long': np.float64(-0.1758), 'officialname': 'Hove'}, {'lat': np.float64(50.85), 'long': np.float64(0.57), 'officialname': 'Hastings'}, {'lat': np.float64(51.655), 'long': np.float64(-0.3957), 'officialname': 'Watford'}, {'lat': np.float64(51.9017), 'long': np.float64(-0.2019), 'officialname': 'Stevenage'}, {'lat': np.float64(54.69), 'long': np.float64(-1.21), 'officialname': 'Hartlepool'}, {'lat': np.float64(53.19), 'long': np.float64(-2.89), 'officialname': 'Chester'}, {'lat': np.float64(51.4828), 'long': np.float64(-0.195), 'officialname': 'Fulham'}, {'lat': np.float64(52.523), 'long': np.float64(-1.468), 'officialname': 'Nuneaton'}, {'lat': np.float64(51.5175), 'long': np.float64(-0.2988), 'officialname': 'Ealing'}, {'lat': np.float64(51.8168), 'long': np.float64(-0.8124), 'officialname': 'Aylesbury'}, {'lat': np.float64(51.6154), 'long': np.float64(-0.0708), 'officialname': 'Edmonton'}, {'lat': np.float64(51.755), 'long': np.float64(-0.336), 'officialname': 'Saint Albans'}, {'lat': np.float64(53.789), 'long': np.float64(-2.248), 'officialname': 'Burnley'}, {'lat': np.float64(53.7167), 'long': np.float64(-1.6356), 'officialname': 'Batley'}, {'lat': np.float64(53.5809), 'long': np.float64(-0.6502), 'officialname': 'Scunthorpe'}, {'lat': np.float64(52.508), 'long': np.float64(-2.089), 'officialname': 'Dudley'}, {'lat': np.float64(51.4575), 'long': np.float64(-0.1175), 'officialname': 'Brixton'}, {'lat': np.float64(51.5111), 'long': np.float64(-0.3756), 'officialname': 'Southall'}, {'lat': np.float64(55.8456), 'long': np.float64(-4.4239), 'officialname': 'Paisley'}, {'lat': np.float64(51.37), 'long': np.float64(0.52), 'officialname': 'Chatham'}, {'lat': np.float64(51.5323), 'long': np.float64(0.0554), 'officialname': 'East Ham'}, {'lat': np.float64(51.346), 'long': np.float64(-2.977), 'officialname': 'Weston-super-Mare'}, {'lat': np.float64(54.8947), 'long': np.float64(-2.9364), 'officialname': 'Carlisle'}, {'lat': np.float64(54.995), 'long': np.float64(-1.43), 'officialname': 'South Shields'}, {'lat': np.float64(55.7644), 'long': np.float64(-4.1769), 'officialname': 'East Kilbride'}, {'lat': np.float64(52.8019), 'long': np.float64(-1.6367), 'officialname': 'Burton upon Trent'}, {'lat': np.float64(53.9919), 'long': np.float64(-1.5378), 'officialname': 'Harrogate'}, {'lat': np.float64(53.099), 'long': np.float64(-2.44), 'officialname': 'Crewe'}, {'lat': np.float64(52.48), 'long': np.float64(1.75), 'officialname': 'Lowestoft'}, {'lat': np.float64(52.37), 'long': np.float64(-1.26), 'officialname': 'Rugby'}, {'lat': np.float64(51.623), 'long': np.float64(0.009), 'officialname': 'Chingford'}, {'lat': np.float64(51.5404), 'long': np.float64(-0.4778), 'officialname': 'Uxbridge'}, {'lat': np.float64(52.58), 'long': np.float64(-1.98), 'officialname': 'Walsall'}, {'lat': np.float64(51.475), 'long': np.float64(0.33), 'officialname': 'Grays'}, {'lat': np.float64(51.3868), 'long': np.float64(-0.4133), 'officialname': 'Walton upon Thames'}, {'lat': np.float64(51.4002), 'long': np.float64(-0.1086), 'officialname': 'Thornton Heath'}, {'lat': np.float64(51.599), 'long': np.float64(-0.187), 'officialname': 'Finchley'}, {'lat': np.float64(51.5), 'long': np.float64(-0.19), 'officialname': 'Kensington'}, {'lat': np.float64(52.974), 'long': np.float64(-0.0214), 'officialname': 'Boston'}, {'lat': np.float64(50.4353), 'long': np.float64(-3.5625), 'officialname': 'Paignton'}, {'lat': np.float64(50.88), 'long': np.float64(-1.03), 'officialname': 'Waterlooville'}, {'lat': np.float64(53.875), 'long': np.float64(-1.706), 'officialname': 'Guiseley'}, {'lat': np.float64(51.5565), 'long': np.float64(0.2128), 'officialname': 'Hornchurch'}, {'lat': np.float64(51.4009), 'long': np.float64(-0.1517), 'officialname': 'Mitcham'}, {'lat': np.float64(51.4496), 'long': np.float64(-0.4089), 'officialname': 'Feltham'}, {'lat': np.float64(52.4575), 'long': np.float64(-2.1479), 'officialname': 'Stourbridge'}, {'lat': np.float64(51.375), 'long': np.float64(0.5), 'officialname': 'Rochester'}, {'lat': np.float64(53.691), 'long': np.float64(-1.633), 'officialname': 'Dewsbury'}, {'lat': np.float64(51.5135), 'long': np.float64(-0.2707), 'officialname': 'Acton'}, {'lat': np.float64(51.449), 'long': np.float64(-0.337), 'officialname': 'Twickenham'}, {'lat': np.float64(53.046), 'long': np.float64(-2.993), 'officialname': 'Wrecsam'}, {'lat': np.float64(53.279), 'long': np.float64(-2.897), 'officialname': 'Ellesmere Port'}, {'lat': np.float64(54.66), 'long': np.float64(-5.67), 'officialname': 'Bangor'}, {'lat': np.float64(51.019), 'long': np.float64(-3.1), 'officialname': 'Taunton'}, {'lat': np.float64(52.7725), 'long': np.float64(-1.2078), 'officialname': 'Loughborough'}, {'lat': np.float64(51.54), 'long': np.float64(0.08), 'officialname': 'Barking'}, {'lat': np.float64(51.6185), 'long': np.float64(-0.2729), 'officialname': 'Edgware'}, {'lat': np.float64(50.8094), 'long': np.float64(-0.5409), 'officialname': 'Littlehampton'}, {'lat': np.float64(51.576), 'long': np.float64(-0.433), 'officialname': 'Ruislip'}, {'lat': np.float64(51.4279), 'long': np.float64(-0.1235), 'officialname': 'Streatham'}, {'lat': np.float64(51.132), 'long': np.float64(0.263), 'officialname': 'Royal Tunbridge Wells'}, {'lat': np.float64(53.35), 'long': np.float64(-3.003), 'officialname': 'Bebington'}, {'lat': np.float64(53.25), 'long': np.float64(-2.13), 'officialname': 'Macclesfield'}, {'lat': np.float64(52.3028), 'long': np.float64(-0.6944), 'officialname': 'Wellingborough'}, {'lat': np.float64(52.3931), 'long': np.float64(-0.7229), 'officialname': 'Kettering'}, {'lat': np.float64(51.878), 'long': np.float64(0.55), 'officialname': 'Braintree'}, {'lat': np.float64(52.2919), 'long': np.float64(-1.5358), 'officialname': 'Royal Leamington Spa'}, {'lat': np.float64(54.1108), 'long': np.float64(-3.2261), 'officialname': 'Barrow in Furness'}, {'lat': np.float64(56.0719), 'long': np.float64(-3.4393), 'officialname': 'Dunfermline'}, {'lat': np.float64(53.3838), 'long': np.float64(-2.3547), 'officialname': 'Altrincham'}, {'lat': np.float64(54.0489), 'long': np.float64(-2.8014), 'officialname': 'Lancaster'}, {'lat': np.float64(53.4872), 'long': np.float64(-3.0343), 'officialname': 'Crosby'}, {'lat': np.float64(53.4457), 'long': np.float64(-2.9891), 'officialname': 'Bootle'}, {'lat': np.float64(51.5423), 'long': np.float64(-0.0026), 'officialname': 'Stratford'}, {'lat': np.float64(51.0792), 'long': np.float64(1.1794), 'officialname': 'Folkestone'}, {'lat': np.float64(55.945), 'long': np.float64(-3.994), 'officialname': 'Cumbernauld'}, {'lat': np.float64(51.208), 'long': np.float64(-1.48), 'officialname': 'Andover'}, {'lat': np.float64(51.66), 'long': np.float64(-3.81), 'officialname': 'Neath'}, {'lat': np.float64(52.488), 'long': np.float64(-2.05), 'officialname': 'Rowley Regis'}, {'lat': np.float64(54.2825), 'long': np.float64(-0.4), 'officialname': 'Scarborough'}, {'lat': np.float64(55.98), 'long': np.float64(-3.17), 'officialname': 'Leith'}, {'lat': np.float64(50.9452), 'long': np.float64(-2.637), 'officialname': 'Yeovil'}, {'lat': np.float64(51.451), 'long': np.float64(0.052), 'officialname': 'Eltham'}, {'lat': np.float64(51.5541), 'long': np.float64(-0.1744), 'officialname': 'Hampstead'}, {'lat': np.float64(53.125), 'long': np.float64(-1.261), 'officialname': 'Sutton in Ashfield'}, {'lat': np.float64(51.4015), 'long': np.float64(-0.1949), 'officialname': 'Morden'}, {'lat': np.float64(51.6444), 'long': np.float64(-0.1997), 'officialname': 'Barnet'}, {'lat': np.float64(53.4466), 'long': np.float64(-2.3086), 'officialname': 'Stretford'}, {'lat': np.float64(51.408), 'long': np.float64(-0.022), 'officialname': 'Beckenham'}, {'lat': np.float64(51.5299), 'long': np.float64(-0.3488), 'officialname': 'Greenford'}, {'lat': np.float64(51.702), 'long': np.float64(-0.035), 'officialname': 'Cheshunt'}, {'lat': np.float64(53.48), 'long': np.float64(-2.89), 'officialname': 'Kirkby'}, {'lat': np.float64(51.07), 'long': np.float64(-1.79), 'officialname': 'Salisbury'}, {'lat': np.float64(53.4897), 'long': np.float64(-2.0952), 'officialname': 'Ashton'}, {'lat': np.float64(51.394), 'long': np.float64(-0.307), 'officialname': 'Surbiton'}, {'lat': np.float64(53.716), 'long': np.float64(-1.356), 'officialname': 'Castleford'}, {'lat': np.float64(51.4452), 'long': np.float64(-0.0207), 'officialname': 'Catford'}, {'lat': np.float64(53.3042), 'long': np.float64(-1.1244), 'officialname': 'Worksop'}, {'lat': np.float64(53.7492), 'long': np.float64(-1.6023), 'officialname': 'Morley'}, {'lat': np.float64(51.743), 'long': np.float64(-3.378), 'officialname': 'Merthyr Tudful'}, {'lat': np.float64(53.555), 'long': np.float64(-2.187), 'officialname': 'Middleton'}, {'lat': np.float64(51.2834), 'long': np.float64(-0.8456), 'officialname': 'Fleet'}, {'lat': np.float64(50.85), 'long': np.float64(-1.18), 'officialname': 'Fareham'}, {'lat': np.float64(53.4487), 'long': np.float64(-2.3747), 'officialname': 'Urmston'}, {'lat': np.float64(51.3656), 'long': np.float64(-0.1963), 'officialname': 'Sutton'}, {'lat': np.float64(51.578), 'long': np.float64(-3.218), 'officialname': 'Caerphilly'}, {'lat': np.float64(51.128), 'long': np.float64(-2.993), 'officialname': 'Bridgwater'}, {'lat': np.float64(51.401), 'long': np.float64(-1.323), 'officialname': 'Newbury'}, {'lat': np.float64(51.4594), 'long': np.float64(0.1097), 'officialname': 'Welling'}, {'lat': np.float64(51.46), 'long': np.float64(-2.505), 'officialname': 'Kingswood'}, {'lat': np.float64(51.886), 'long': np.float64(-0.521), 'officialname': 'Dunstable'}, {'lat': np.float64(51.336), 'long': np.float64(1.416), 'officialname': 'Ramsgate'}, {'lat': np.float64(51.393), 'long': np.float64(0.478), 'officialname': 'Strood'}, {'lat': np.float64(53.5533), 'long': np.float64(-0.0215), 'officialname': 'Cleethorpes'}, {'lat': np.float64(51.5932), 'long': np.float64(-0.3894), 'officialname': 'Pinner'}, {'lat': np.float64(52.606), 'long': np.float64(1.729), 'officialname': 'Great Yarmouth'}, {'lat': np.float64(52.9711), 'long': np.float64(-1.3092), 'officialname': 'Ilkeston'}, {'lat': np.float64(53.653), 'long': np.float64(-2.632), 'officialname': 'Chorley'}, {'lat': np.float64(51.37), 'long': np.float64(1.13), 'officialname': 'Herne Bay'}, {'lat': np.float64(51.872), 'long': np.float64(0.1725), 'officialname': 'Bishops Stortford'}, {'lat': np.float64(53.005), 'long': np.float64(-1.127), 'officialname': 'Arnold'}, {'lat': np.float64(52.724), 'long': np.float64(-1.369), 'officialname': 'Coalville'}, {'lat': np.float64(51.994), 'long': np.float64(-0.732), 'officialname': 'Bletchley'}, {'lat': np.float64(51.9165), 'long': np.float64(-0.6617), 'officialname': 'Leighton Buzzard'}, {'lat': np.float64(55.86), 'long': np.float64(-3.98), 'officialname': 'Airdrie'}, {'lat': np.float64(55.126), 'long': np.float64(-1.514), 'officialname': 'Blyth'}, {'lat': np.float64(51.574), 'long': np.float64(0.4181), 'officialname': 'Laindon'}, {'lat': np.float64(51.684), 'long': np.float64(-4.163), 'officialname': 'Llanelli'}, {'lat': np.float64(52.927), 'long': np.float64(-1.215), 'officialname': 'Beeston'}, {'lat': np.float64(52.4629), 'long': np.float64(-1.8542), 'officialname': 'Small Heath'}, {'lat': np.float64(55.0456), 'long': np.float64(-1.4443), 'officialname': 'Whitley Bay'}, {'lat': np.float64(53.4554), 'long': np.float64(-2.1122), 'officialname': 'Denton'}, {'lat': np.float64(52.932), 'long': np.float64(-1.127), 'officialname': 'West Bridgford'}, {'lat': np.float64(51.6578), 'long': np.float64(-0.2722), 'officialname': 'Borehamwood'}, {'lat': np.float64(56.0011), 'long': np.float64(-3.7835), 'officialname': 'Falkirk'}, {'lat': np.float64(53.5239), 'long': np.float64(-2.3991), 'officialname': 'Walkden'}, {'lat': np.float64(51.5878), 'long': np.float64(-0.3086), 'officialname': 'Kenton'}, {'lat': np.float64(54.0819), 'long': np.float64(-0.1923), 'officialname': 'Bridlington'}, {'lat': np.float64(54.61), 'long': np.float64(-1.27), 'officialname': 'Billingham'}, {'lat': np.float64(52.918), 'long': np.float64(-0.638), 'officialname': 'Grantham'}, {'lat': np.float64(55.0097), 'long': np.float64(-1.4448), 'officialname': 'North Shields'}, {'lat': np.float64(51.947), 'long': np.float64(-0.283), 'officialname': 'Hitchin'}, {'lat': np.float64(52.7858), 'long': np.float64(-0.1529), 'officialname': 'Spalding'}, {'lat': np.float64(51.36), 'long': np.float64(0.61), 'officialname': 'Rainham'}, {'lat': np.float64(51.978), 'long': np.float64(-0.23), 'officialname': 'Letchworth'}, {'lat': np.float64(51.6114), 'long': np.float64(0.5207), 'officialname': 'Wickford'}, {'lat': np.float64(53.4111), 'long': np.float64(-2.8403), 'officialname': 'Huyton'}, {'lat': np.float64(51.6717), 'long': np.float64(-1.2783), 'officialname': 'Abingdon'}, {'lat': np.float64(51.32), 'long': np.float64(-2.208), 'officialname': 'Trowbridge'}, {'lat': np.float64(52.5812), 'long': np.float64(-1.093), 'officialname': 'Wigston Magna'}, {'lat': np.float64(51.606), 'long': np.float64(-1.241), 'officialname': 'Didcot'}, {'lat': np.float64(51.433), 'long': np.float64(-0.933), 'officialname': 'Earley'}, {'lat': np.float64(51.459), 'long': np.float64(0.138), 'officialname': 'Bexleyheath'}, {'lat': np.float64(53.4429), 'long': np.float64(-1.4698), 'officialname': 'Ecclesfield'}, {'lat': np.float64(53.698), 'long': np.float64(-2.461), 'officialname': 'Darwen'}, {'lat': np.float64(53.5333), 'long': np.float64(-2.2833), 'officialname': 'Prestwich'}, {'lat': np.float64(51.602), 'long': np.float64(-3.342), 'officialname': 'Pontypridd'}, {'lat': np.float64(55.828), 'long': np.float64(-4.214), 'officialname': 'Rutherglen'}, {'lat': np.float64(51.1295), 'long': np.float64(1.3089), 'officialname': 'Dover'}, {'lat': np.float64(50.8365), 'long': np.float64(-0.7792), 'officialname': 'Chichester'}, {'lat': np.float64(51.2226), 'long': np.float64(1.4006), 'officialname': 'Deal'}, {'lat': np.float64(51.9), 'long': np.float64(-1.15), 'officialname': 'Bicester'}, {'lat': np.float64(51.5467), 'long': np.float64(-0.37), 'officialname': 'Northolt'}, {'lat': np.float64(55.7742), 'long': np.float64(-3.9183), 'officialname': 'Wishaw'}, {'lat': np.float64(51.3652), 'long': np.float64(-0.1676), 'officialname': 'Carshalton'}, {'lat': np.float64(53.001), 'long': np.float64(-1.197), 'officialname': 'Bulwell'}, {'lat': np.float64(54.591), 'long': np.float64(-5.68), 'officialname': 'Newtownards'}, {'lat': np.float64(54.326), 'long': np.float64(-2.745), 'officialname': 'Kendal'}, {'lat': np.float64(55.082), 'long': np.float64(-1.585), 'officialname': 'Cramlington'}, {'lat': np.float64(52.3353), 'long': np.float64(-2.0579), 'officialname': 'Bromsgrove'}, {'lat': np.float64(51.703), 'long': np.float64(-3.041), 'officialname': 'Pont-y-p≈µl'}, {'lat': np.float64(51.509), 'long': np.float64(-0.338), 'officialname': 'Hanwell'}, {'lat': np.float64(51.2279), 'long': np.float64(-2.3215), 'officialname': 'Frome'}, {'lat': np.float64(51.5981), 'long': np.float64(-0.1149), 'officialname': 'Wood Green'}, {'lat': np.float64(52.5708), 'long': np.float64(-2.0457), 'officialname': 'Darlaston'}, {'lat': np.float64(55.181), 'long': np.float64(-1.568), 'officialname': 'Ashington'}, {'lat': np.float64(52.9877), 'long': np.float64(-2.1327), 'officialname': 'Longton'}, {'lat': np.float64(52.7661), 'long': np.float64(-0.886), 'officialname': 'Melton Mowbray'}, {'lat': np.float64(52.606), 'long': np.float64(-1.9179), 'officialname': 'Aldridge'}, {'lat': np.float64(53.5452), 'long': np.float64(-2.3999), 'officialname': 'Farnworth'}, {'lat': np.float64(51.552), 'long': np.float64(-0.097), 'officialname': 'Highbury'}, {'lat': np.float64(53.3761), 'long': np.float64(-2.1897), 'officialname': 'Cheadle Hulme'}, {'lat': np.float64(54.62), 'long': np.float64(-1.58), 'officialname': 'Newton Aycliffe'}, {'lat': np.float64(52.4299), 'long': np.float64(-1.9355), 'officialname': 'Bournville'}, {'lat': np.float64(52.009), 'long': np.float64(-0.789), 'officialname': 'Shenley Brook End'}, {'lat': np.float64(54.85), 'long': np.float64(-1.83), 'officialname': 'Consett'}, {'lat': np.float64(51.3211), 'long': np.float64(-0.1386), 'officialname': 'Coulsdon'}, {'lat': np.float64(52.566), 'long': np.float64(-2.0728), 'officialname': 'Bilston'}, {'lat': np.float64(52.7001), 'long': np.float64(-2.5157), 'officialname': 'Wellington'}, {'lat': np.float64(54.663), 'long': np.float64(-1.676), 'officialname': 'Bishop Auckland'}, {'lat': np.float64(52.395), 'long': np.float64(-1.979), 'officialname': 'Longbridge'}, {'lat': np.float64(52.614), 'long': np.float64(-2.004), 'officialname': 'Bloxwich'}, {'lat': np.float64(51.5557), 'long': np.float64(0.2512), 'officialname': 'Upminster'}, {'lat': np.float64(53.321), 'long': np.float64(-3.48), 'officialname': 'Rhyl'}, {'lat': np.float64(52.267), 'long': np.float64(-2.153), 'officialname': 'Droitwich'}, {'lat': np.float64(53.5355), 'long': np.float64(-2.5658), 'officialname': 'Hindley'}, {'lat': np.float64(53.549), 'long': np.float64(-2.529), 'officialname': 'Westhoughton'}, {'lat': np.float64(51.3589), 'long': np.float64(1.4394), 'officialname': 'Broadstairs'} ]</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -2173,13 +2167,8 @@
         <f t="shared" si="0"/>
         <v>{'lat': np.float64(50.8058), 'long': np.float64(-1.0872), 'officialname': 'Portsmouth'}</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="L4" s="1" t="str">
-        <f>LEFT(L3,LEN(L3)-1)</f>
-        <v>[{'lat': np.float64(51.5072), 'long': np.float64(-0.1275), 'officialname': 'London'}, {'lat': np.float64(52.48), 'long': np.float64(-1.9025), 'officialname': 'Birmingham'}, {'lat': np.float64(50.8058), 'long': np.float64(-1.0872), 'officialname': 'Portsmouth'}, {'lat': np.float64(50.9025), 'long': np.float64(-1.4042), 'officialname': 'Southampton'}, {'lat': np.float64(52.9561), 'long': np.float64(-1.1512), 'officialname': 'Nottingham'}, {'lat': np.float64(51.4536), 'long': np.float64(-2.5975), 'officialname': 'Bristol'}, {'lat': np.float64(53.479), 'long': np.float64(-2.2452), 'officialname': 'Manchester'}, {'lat': np.float64(53.4094), 'long': np.float64(-2.9785), 'officialname': 'Liverpool'}, {'lat': np.float64(52.6344), 'long': np.float64(-1.1319), 'officialname': 'Leicester'}, {'lat': np.float64(50.8147), 'long': np.float64(-0.3714), 'officialname': 'Worthing'}, {'lat': np.float64(52.4081), 'long': np.float64(-1.5106), 'officialname': 'Coventry'}, {'lat': np.float64(54.5964), 'long': np.float64(-5.93), 'officialname': 'Belfast'}, {'lat': np.float64(53.8), 'long': np.float64(-1.75), 'officialname': 'Bradford'}, {'lat': np.float64(52.9247), 'long': np.float64(-1.478), 'officialname': 'Derby'}, {'lat': np.float64(50.3714), 'long': np.float64(-4.1422), 'officialname': 'Plymouth'}, {'lat': np.float64(51.4947), 'long': np.float64(-0.1353), 'officialname': 'Westminster'}, {'lat': np.float64(52.5833), 'long': np.float64(-2.1333), 'officialname': 'Wolverhampton'}, {'lat': np.float64(52.2304), 'long': np.float64(-0.8938), 'officialname': 'Northampton'}, {'lat': np.float64(52.6286), 'long': np.float64(1.2928), 'officialname': 'Norwich'}, {'lat': np.float64(51.8783), 'long': np.float64(-0.4147), 'officialname': 'Luton'}, {'lat': np.float64(52.413), 'long': np.float64(-1.778), 'officialname': 'Solihull'}, {'lat': np.float64(51.544), 'long': np.float64(-0.1027), 'officialname': 'Islington'}, {'lat': np.float64(57.15), 'long': np.float64(-2.11), 'officialname': 'Aberdeen'}, {'lat': np.float64(51.3727), 'long': np.float64(-0.1099), 'officialname': 'Croydon'}, {'lat': np.float64(50.72), 'long': np.float64(-1.88), 'officialname': 'Bournemouth'}, {'lat': np.float64(51.58), 'long': np.float64(0.49), 'officialname': 'Basildon'}, {'lat': np.float64(51.272), 'long': np.float64(0.529), 'officialname': 'Maidstone'}, {'lat': np.float64(51.5575), 'long': np.float64(0.0858), 'officialname': 'Ilford'}, {'lat': np.float64(53.39), 'long': np.float64(-2.59), 'officialname': 'Warrington'}, {'lat': np.float64(51.75), 'long': np.float64(-1.25), 'officialname': 'Oxford'}, {'lat': np.float64(51.5836), 'long': np.float64(-0.3464), 'officialname': 'Harrow'}, {'lat': np.float64(52.519), 'long': np.float64(-1.995), 'officialname': 'West Bromwich'}, {'lat': np.float64(51.8667), 'long': np.float64(-2.25), 'officialname': 'Gloucester'}, {'lat': np.float64(53.96), 'long': np.float64(-1.08), 'officialname': 'York'}, {'lat': np.float64(53.8142), 'long': np.float64(-3.0503), 'officialname': 'Blackpool'}, {'lat': np.float64(53.4083), 'long': np.float64(-2.1494), 'officialname': 'Stockport'}, {'lat': np.float64(53.424), 'long': np.float64(-2.322), 'officialname': 'Sale'}, {'lat': np.float64(51.5975), 'long': np.float64(-0.0681), 'officialname': 'Tottenham'}, {'lat': np.float64(52.2053), 'long': np.float64(0.1192), 'officialname': 'Cambridge'}, {'lat': np.float64(51.5768), 'long': np.float64(0.1801), 'officialname': 'Romford'}, {'lat': np.float64(51.8917), 'long': np.float64(0.903), 'officialname': 'Colchester'}, {'lat': np.float64(51.6287), 'long': np.float64(-0.7482), 'officialname': 'High Wycombe'}, {'lat': np.float64(54.9556), 'long': np.float64(-1.6), 'officialname': 'Gateshead'}, {'lat': np.float64(51.5084), 'long': np.float64(-0.5881), 'officialname': 'Slough'}, {'lat': np.float64(53.748), 'long': np.float64(-2.482), 'officialname': 'Blackburn'}, {'lat': np.float64(51.73), 'long': np.float64(0.48), 'officialname': 'Chelmsford'}, {'lat': np.float64(53.61), 'long': np.float64(-2.16), 'officialname': 'Rochdale'}, {'lat': np.float64(53.43), 'long': np.float64(-1.357), 'officialname': 'Rotherham'}, {'lat': np.float64(51.584), 'long': np.float64(-0.021), 'officialname': 'Walthamstow'}, {'lat': np.float64(51.2667), 'long': np.float64(-1.0876), 'officialname': 'Basingstoke'}, {'lat': np.float64(53.483), 'long': np.float64(-2.2931), 'officialname': 'Salford'}, {'lat': np.float64(51.4668), 'long': np.float64(-0.375), 'officialname': 'Hounslow'}, {'lat': np.float64(51.5528), 'long': np.float64(-0.2979), 'officialname': 'Wembley'}, {'lat': np.float64(52.1911), 'long': np.float64(-2.2206), 'officialname': 'Worcester'}, {'lat': np.float64(51.4928), 'long': np.float64(-0.2229), 'officialname': 'Hammersmith'}, {'lat': np.float64(51.5864), 'long': np.float64(0.6049), 'officialname': 'Rayleigh'}, {'lat': np.float64(51.7526), 'long': np.float64(-0.4692), 'officialname': 'Hemel Hempstead'}, {'lat': np.float64(51.38), 'long': np.float64(-2.36), 'officialname': 'Bath'}, {'lat': np.float64(51.5127), 'long': np.float64(-0.4211), 'officialname': 'Hayes'}, {'lat': np.float64(54.527), 'long': np.float64(-1.5526), 'officialname': 'Darlington'}, {'lat': np.float64(50.8352), 'long': np.float64(-0.1758), 'officialname': 'Hove'}, {'lat': np.float64(50.85), 'long': np.float64(0.57), 'officialname': 'Hastings'}, {'lat': np.float64(51.655), 'long': np.float64(-0.3957), 'officialname': 'Watford'}, {'lat': np.float64(51.9017), 'long': np.float64(-0.2019), 'officialname': 'Stevenage'}, {'lat': np.float64(54.69), 'long': np.float64(-1.21), 'officialname': 'Hartlepool'}, {'lat': np.float64(53.19), 'long': np.float64(-2.89), 'officialname': 'Chester'}, {'lat': np.float64(51.4828), 'long': np.float64(-0.195), 'officialname': 'Fulham'}, {'lat': np.float64(52.523), 'long': np.float64(-1.468), 'officialname': 'Nuneaton'}, {'lat': np.float64(51.5175), 'long': np.float64(-0.2988), 'officialname': 'Ealing'}, {'lat': np.float64(51.8168), 'long': np.float64(-0.8124), 'officialname': 'Aylesbury'}, {'lat': np.float64(51.6154), 'long': np.float64(-0.0708), 'officialname': 'Edmonton'}, {'lat': np.float64(51.755), 'long': np.float64(-0.336), 'officialname': 'Saint Albans'}, {'lat': np.float64(53.789), 'long': np.float64(-2.248), 'officialname': 'Burnley'}, {'lat': np.float64(53.7167), 'long': np.float64(-1.6356), 'officialname': 'Batley'}, {'lat': np.float64(53.5809), 'long': np.float64(-0.6502), 'officialname': 'Scunthorpe'}, {'lat': np.float64(52.508), 'long': np.float64(-2.089), 'officialname': 'Dudley'}, {'lat': np.float64(51.4575), 'long': np.float64(-0.1175), 'officialname': 'Brixton'}, {'lat': np.float64(51.5111), 'long': np.float64(-0.3756), 'officialname': 'Southall'}, {'lat': np.float64(55.8456), 'long': np.float64(-4.4239), 'officialname': 'Paisley'}, {'lat': np.float64(51.37), 'long': np.float64(0.52), 'officialname': 'Chatham'}, {'lat': np.float64(51.5323), 'long': np.float64(0.0554), 'officialname': 'East Ham'}, {'lat': np.float64(51.346), 'long': np.float64(-2.977), 'officialname': 'Weston-super-Mare'}, {'lat': np.float64(54.8947), 'long': np.float64(-2.9364), 'officialname': 'Carlisle'}, {'lat': np.float64(54.995), 'long': np.float64(-1.43), 'officialname': 'South Shields'}, {'lat': np.float64(55.7644), 'long': np.float64(-4.1769), 'officialname': 'East Kilbride'}, {'lat': np.float64(52.8019), 'long': np.float64(-1.6367), 'officialname': 'Burton upon Trent'}, {'lat': np.float64(53.9919), 'long': np.float64(-1.5378), 'officialname': 'Harrogate'}, {'lat': np.float64(53.099), 'long': np.float64(-2.44), 'officialname': 'Crewe'}, {'lat': np.float64(52.48), 'long': np.float64(1.75), 'officialname': 'Lowestoft'}, {'lat': np.float64(52.37), 'long': np.float64(-1.26), 'officialname': 'Rugby'}, {'lat': np.float64(51.623), 'long': np.float64(0.009), 'officialname': 'Chingford'}, {'lat': np.float64(51.5404), 'long': np.float64(-0.4778), 'officialname': 'Uxbridge'}, {'lat': np.float64(52.58), 'long': np.float64(-1.98), 'officialname': 'Walsall'}, {'lat': np.float64(51.475), 'long': np.float64(0.33), 'officialname': 'Grays'}, {'lat': np.float64(51.3868), 'long': np.float64(-0.4133), 'officialname': 'Walton upon Thames'}, {'lat': np.float64(51.4002), 'long': np.float64(-0.1086), 'officialname': 'Thornton Heath'}, {'lat': np.float64(51.599), 'long': np.float64(-0.187), 'officialname': 'Finchley'}, {'lat': np.float64(51.5), 'long': np.float64(-0.19), 'officialname': 'Kensington'}, {'lat': np.float64(52.974), 'long': np.float64(-0.0214), 'officialname': 'Boston'}, {'lat': np.float64(50.4353), 'long': np.float64(-3.5625), 'officialname': 'Paignton'}, {'lat': np.float64(50.88), 'long': np.float64(-1.03), 'officialname': 'Waterlooville'}, {'lat': np.float64(53.875), 'long': np.float64(-1.706), 'officialname': 'Guiseley'}, {'lat': np.float64(51.5565), 'long': np.float64(0.2128), 'officialname': 'Hornchurch'}, {'lat': np.float64(51.4009), 'long': np.float64(-0.1517), 'officialname': 'Mitcham'}, {'lat': np.float64(51.4496), 'long': np.float64(-0.4089), 'officialname': 'Feltham'}, {'lat': np.float64(52.4575), 'long': np.float64(-2.1479), 'officialname': 'Stourbridge'}, {'lat': np.float64(51.375), 'long': np.float64(0.5), 'officialname': 'Rochester'}, {'lat': np.float64(53.691), 'long': np.float64(-1.633), 'officialname': 'Dewsbury'}, {'lat': np.float64(51.5135), 'long': np.float64(-0.2707), 'officialname': 'Acton'}, {'lat': np.float64(51.449), 'long': np.float64(-0.337), 'officialname': 'Twickenham'}, {'lat': np.float64(53.046), 'long': np.float64(-2.993), 'officialname': 'Wrecsam'}, {'lat': np.float64(53.279), 'long': np.float64(-2.897), 'officialname': 'Ellesmere Port'}, {'lat': np.float64(54.66), 'long': np.float64(-5.67), 'officialname': 'Bangor'}, {'lat': np.float64(51.019), 'long': np.float64(-3.1), 'officialname': 'Taunton'}, {'lat': np.float64(52.7725), 'long': np.float64(-1.2078), 'officialname': 'Loughborough'}, {'lat': np.float64(51.54), 'long': np.float64(0.08), 'officialname': 'Barking'}, {'lat': np.float64(51.6185), 'long': np.float64(-0.2729), 'officialname': 'Edgware'}, {'lat': np.float64(50.8094), 'long': np.float64(-0.5409), 'officialname': 'Littlehampton'}, {'lat': np.float64(51.576), 'long': np.float64(-0.433), 'officialname': 'Ruislip'}, {'lat': np.float64(51.4279), 'long': np.float64(-0.1235), 'officialname': 'Streatham'}, {'lat': np.float64(51.132), 'long': np.float64(0.263), 'officialname': 'Royal Tunbridge Wells'}, {'lat': np.float64(53.35), 'long': np.float64(-3.003), 'officialname': 'Bebington'}, {'lat': np.float64(53.25), 'long': np.float64(-2.13), 'officialname': 'Macclesfield'}, {'lat': np.float64(52.3028), 'long': np.float64(-0.6944), 'officialname': 'Wellingborough'}, {'lat': np.float64(52.3931), 'long': np.float64(-0.7229), 'officialname': 'Kettering'}, {'lat': np.float64(51.878), 'long': np.float64(0.55), 'officialname': 'Braintree'}, {'lat': np.float64(52.2919), 'long': np.float64(-1.5358), 'officialname': 'Royal Leamington Spa'}, {'lat': np.float64(54.1108), 'long': np.float64(-3.2261), 'officialname': 'Barrow in Furness'}, {'lat': np.float64(56.0719), 'long': np.float64(-3.4393), 'officialname': 'Dunfermline'}, {'lat': np.float64(53.3838), 'long': np.float64(-2.3547), 'officialname': 'Altrincham'}, {'lat': np.float64(54.0489), 'long': np.float64(-2.8014), 'officialname': 'Lancaster'}, {'lat': np.float64(53.4872), 'long': np.float64(-3.0343), 'officialname': 'Crosby'}, {'lat': np.float64(53.4457), 'long': np.float64(-2.9891), 'officialname': 'Bootle'}, {'lat': np.float64(51.5423), 'long': np.float64(-0.0026), 'officialname': 'Stratford'}, {'lat': np.float64(51.0792), 'long': np.float64(1.1794), 'officialname': 'Folkestone'}, {'lat': np.float64(55.945), 'long': np.float64(-3.994), 'officialname': 'Cumbernauld'}, {'lat': np.float64(51.208), 'long': np.float64(-1.48), 'officialname': 'Andover'}, {'lat': np.float64(51.66), 'long': np.float64(-3.81), 'officialname': 'Neath'}, {'lat': np.float64(52.488), 'long': np.float64(-2.05), 'officialname': 'Rowley Regis'}, {'lat': np.float64(54.2825), 'long': np.float64(-0.4), 'officialname': 'Scarborough'}, {'lat': np.float64(55.98), 'long': np.float64(-3.17), 'officialname': 'Leith'}, {'lat': np.float64(50.9452), 'long': np.float64(-2.637), 'officialname': 'Yeovil'}, {'lat': np.float64(51.451), 'long': np.float64(0.052), 'officialname': 'Eltham'}, {'lat': np.float64(51.5541), 'long': np.float64(-0.1744), 'officialname': 'Hampstead'}, {'lat': np.float64(53.125), 'long': np.float64(-1.261), 'officialname': 'Sutton in Ashfield'}, {'lat': np.float64(51.4015), 'long': np.float64(-0.1949), 'officialname': 'Morden'}, {'lat': np.float64(51.6444), 'long': np.float64(-0.1997), 'officialname': 'Barnet'}, {'lat': np.float64(53.4466), 'long': np.float64(-2.3086), 'officialname': 'Stretford'}, {'lat': np.float64(51.408), 'long': np.float64(-0.022), 'officialname': 'Beckenham'}, {'lat': np.float64(51.5299), 'long': np.float64(-0.3488), 'officialname': 'Greenford'}, {'lat': np.float64(51.702), 'long': np.float64(-0.035), 'officialname': 'Cheshunt'}, {'lat': np.float64(53.48), 'long': np.float64(-2.89), 'officialname': 'Kirkby'}, {'lat': np.float64(51.07), 'long': np.float64(-1.79), 'officialname': 'Salisbury'}, {'lat': np.float64(53.4897), 'long': np.float64(-2.0952), 'officialname': 'Ashton'}, {'lat': np.float64(51.394), 'long': np.float64(-0.307), 'officialname': 'Surbiton'}, {'lat': np.float64(53.716), 'long': np.float64(-1.356), 'officialname': 'Castleford'}, {'lat': np.float64(51.4452), 'long': np.float64(-0.0207), 'officialname': 'Catford'}, {'lat': np.float64(53.3042), 'long': np.float64(-1.1244), 'officialname': 'Worksop'}, {'lat': np.float64(53.7492), 'long': np.float64(-1.6023), 'officialname': 'Morley'}, {'lat': np.float64(51.743), 'long': np.float64(-3.378), 'officialname': 'Merthyr Tudful'}, {'lat': np.float64(53.555), 'long': np.float64(-2.187), 'officialname': 'Middleton'}, {'lat': np.float64(51.2834), 'long': np.float64(-0.8456), 'officialname': 'Fleet'}, {'lat': np.float64(50.85), 'long': np.float64(-1.18), 'officialname': 'Fareham'}, {'lat': np.float64(53.4487), 'long': np.float64(-2.3747), 'officialname': 'Urmston'}, {'lat': np.float64(51.3656), 'long': np.float64(-0.1963), 'officialname': 'Sutton'}, {'lat': np.float64(51.578), 'long': np.float64(-3.218), 'officialname': 'Caerphilly'}, {'lat': np.float64(51.128), 'long': np.float64(-2.993), 'officialname': 'Bridgwater'}, {'lat': np.float64(51.401), 'long': np.float64(-1.323), 'officialname': 'Newbury'}, {'lat': np.float64(51.4594), 'long': np.float64(0.1097), 'officialname': 'Welling'}, {'lat': np.float64(51.46), 'long': np.float64(-2.505), 'officialname': 'Kingswood'}, {'lat': np.float64(51.886), 'long': np.float64(-0.521), 'officialname': 'Dunstable'}, {'lat': np.float64(51.336), 'long': np.float64(1.416), 'officialname': 'Ramsgate'}, {'lat': np.float64(51.393), 'long': np.float64(0.478), 'officialname': 'Strood'}, {'lat': np.float64(53.5533), 'long': np.float64(-0.0215), 'officialname': 'Cleethorpes'}, {'lat': np.float64(51.5932), 'long': np.float64(-0.3894), 'officialname': 'Pinner'}, {'lat': np.float64(52.606), 'long': np.float64(1.729), 'officialname': 'Great Yarmouth'}, {'lat': np.float64(52.9711), 'long': np.float64(-1.3092), 'officialname': 'Ilkeston'}, {'lat': np.float64(53.653), 'long': np.float64(-2.632), 'officialname': 'Chorley'}, {'lat': np.float64(51.37), 'long': np.float64(1.13), 'officialname': 'Herne Bay'}, {'lat': np.float64(51.872), 'long': np.float64(0.1725), 'officialname': 'Bishops Stortford'}, {'lat': np.float64(53.005), 'long': np.float64(-1.127), 'officialname': 'Arnold'}, {'lat': np.float64(52.724), 'long': np.float64(-1.369), 'officialname': 'Coalville'}, {'lat': np.float64(51.994), 'long': np.float64(-0.732), 'officialname': 'Bletchley'}, {'lat': np.float64(51.9165), 'long': np.float64(-0.6617), 'officialname': 'Leighton Buzzard'}, {'lat': np.float64(55.86), 'long': np.float64(-3.98), 'officialname': 'Airdrie'}, {'lat': np.float64(55.126), 'long': np.float64(-1.514), 'officialname': 'Blyth'}, {'lat': np.float64(51.574), 'long': np.float64(0.4181), 'officialname': 'Laindon'}, {'lat': np.float64(51.684), 'long': np.float64(-4.163), 'officialname': 'Llanelli'}, {'lat': np.float64(52.927), 'long': np.float64(-1.215), 'officialname': 'Beeston'}, {'lat': np.float64(52.4629), 'long': np.float64(-1.8542), 'officialname': 'Small Heath'}, {'lat': np.float64(55.0456), 'long': np.float64(-1.4443), 'officialname': 'Whitley Bay'}, {'lat': np.float64(53.4554), 'long': np.float64(-2.1122), 'officialname': 'Denton'}, {'lat': np.float64(52.932), 'long': np.float64(-1.127), 'officialname': 'West Bridgford'}, {'lat': np.float64(51.6578), 'long': np.float64(-0.2722), 'officialname': 'Borehamwood'}, {'lat': np.float64(56.0011), 'long': np.float64(-3.7835), 'officialname': 'Falkirk'}, {'lat': np.float64(53.5239), 'long': np.float64(-2.3991), 'officialname': 'Walkden'}, {'lat': np.float64(51.5878), 'long': np.float64(-0.3086), 'officialname': 'Kenton'}, {'lat': np.float64(54.0819), 'long': np.float64(-0.1923), 'officialname': 'Bridlington'}, {'lat': np.float64(54.61), 'long': np.float64(-1.27), 'officialname': 'Billingham'}, {'lat': np.float64(52.918), 'long': np.float64(-0.638), 'officialname': 'Grantham'}, {'lat': np.float64(55.0097), 'long': np.float64(-1.4448), 'officialname': 'North Shields'}, {'lat': np.float64(51.947), 'long': np.float64(-0.283), 'officialname': 'Hitchin'}, {'lat': np.float64(52.7858), 'long': np.float64(-0.1529), 'officialname': 'Spalding'}, {'lat': np.float64(51.36), 'long': np.float64(0.61), 'officialname': 'Rainham'}, {'lat': np.float64(51.978), 'long': np.float64(-0.23), 'officialname': 'Letchworth'}, {'lat': np.float64(51.6114), 'long': np.float64(0.5207), 'officialname': 'Wickford'}, {'lat': np.float64(53.4111), 'long': np.float64(-2.8403), 'officialname': 'Huyton'}, {'lat': np.float64(51.6717), 'long': np.float64(-1.2783), 'officialname': 'Abingdon'}, {'lat': np.float64(51.32), 'long': np.float64(-2.208), 'officialname': 'Trowbridge'}, {'lat': np.float64(52.5812), 'long': np.float64(-1.093), 'officialname': 'Wigston Magna'}, {'lat': np.float64(51.606), 'long': np.float64(-1.241), 'officialname': 'Didcot'}, {'lat': np.float64(51.433), 'long': np.float64(-0.933), 'officialname': 'Earley'}, {'lat': np.float64(51.459), 'long': np.float64(0.138), 'officialname': 'Bexleyheath'}, {'lat': np.float64(53.4429), 'long': np.float64(-1.4698), 'officialname': 'Ecclesfield'}, {'lat': np.float64(53.698), 'long': np.float64(-2.461), 'officialname': 'Darwen'}, {'lat': np.float64(53.5333), 'long': np.float64(-2.2833), 'officialname': 'Prestwich'}, {'lat': np.float64(51.602), 'long': np.float64(-3.342), 'officialname': 'Pontypridd'}, {'lat': np.float64(55.828), 'long': np.float64(-4.214), 'officialname': 'Rutherglen'}, {'lat': np.float64(51.1295), 'long': np.float64(1.3089), 'officialname': 'Dover'}, {'lat': np.float64(50.8365), 'long': np.float64(-0.7792), 'officialname': 'Chichester'}, {'lat': np.float64(51.2226), 'long': np.float64(1.4006), 'officialname': 'Deal'}, {'lat': np.float64(51.9), 'long': np.float64(-1.15), 'officialname': 'Bicester'}, {'lat': np.float64(51.5467), 'long': np.float64(-0.37), 'officialname': 'Northolt'}, {'lat': np.float64(55.7742), 'long': np.float64(-3.9183), 'officialname': 'Wishaw'}, {'lat': np.float64(51.3652), 'long': np.float64(-0.1676), 'officialname': 'Carshalton'}, {'lat': np.float64(53.001), 'long': np.float64(-1.197), 'officialname': 'Bulwell'}, {'lat': np.float64(54.591), 'long': np.float64(-5.68), 'officialname': 'Newtownards'}, {'lat': np.float64(54.326), 'long': np.float64(-2.745), 'officialname': 'Kendal'}, {'lat': np.float64(55.082), 'long': np.float64(-1.585), 'officialname': 'Cramlington'}, {'lat': np.float64(52.3353), 'long': np.float64(-2.0579), 'officialname': 'Bromsgrove'}, {'lat': np.float64(51.703), 'long': np.float64(-3.041), 'officialname': 'Pont-y-p≈µl'}, {'lat': np.float64(51.509), 'long': np.float64(-0.338), 'officialname': 'Hanwell'}, {'lat': np.float64(51.2279), 'long': np.float64(-2.3215), 'officialname': 'Frome'}, {'lat': np.float64(51.5981), 'long': np.float64(-0.1149), 'officialname': 'Wood Green'}, {'lat': np.float64(52.5708), 'long': np.float64(-2.0457), 'officialname': 'Darlaston'}, {'lat': np.float64(55.181), 'long': np.float64(-1.568), 'officialname': 'Ashington'}, {'lat': np.float64(52.9877), 'long': np.float64(-2.1327), 'officialname': 'Longton'}, {'lat': np.float64(52.7661), 'long': np.float64(-0.886), 'officialname': 'Melton Mowbray'}, {'lat': np.float64(52.606), 'long': np.float64(-1.9179), 'officialname': 'Aldridge'}, {'lat': np.float64(53.5452), 'long': np.float64(-2.3999), 'officialname': 'Farnworth'}, {'lat': np.float64(51.552), 'long': np.float64(-0.097), 'officialname': 'Highbury'}, {'lat': np.float64(53.3761), 'long': np.float64(-2.1897), 'officialname': 'Cheadle Hulme'}, {'lat': np.float64(54.62), 'long': np.float64(-1.58), 'officialname': 'Newton Aycliffe'}, {'lat': np.float64(52.4299), 'long': np.float64(-1.9355), 'officialname': 'Bournville'}, {'lat': np.float64(52.009), 'long': np.float64(-0.789), 'officialname': 'Shenley Brook End'}, {'lat': np.float64(54.85), 'long': np.float64(-1.83), 'officialname': 'Consett'}, {'lat': np.float64(51.3211), 'long': np.float64(-0.1386), 'officialname': 'Coulsdon'}, {'lat': np.float64(52.566), 'long': np.float64(-2.0728), 'officialname': 'Bilston'}, {'lat': np.float64(52.7001), 'long': np.float64(-2.5157), 'officialname': 'Wellington'}, {'lat': np.float64(54.663), 'long': np.float64(-1.676), 'officialname': 'Bishop Auckland'}, {'lat': np.float64(52.395), 'long': np.float64(-1.979), 'officialname': 'Longbridge'}, {'lat': np.float64(52.614), 'long': np.float64(-2.004), 'officialname': 'Bloxwich'}, {'lat': np.float64(51.5557), 'long': np.float64(0.2512), 'officialname': 'Upminster'}, {'lat': np.float64(53.321), 'long': np.float64(-3.48), 'officialname': 'Rhyl'}, {'lat': np.float64(52.267), 'long': np.float64(-2.153), 'officialname': 'Droitwich'}, {'lat': np.float64(53.5355), 'long': np.float64(-2.5658), 'officialname': 'Hindley'}, {'lat': np.float64(53.549), 'long': np.float64(-2.529), 'officialname': 'Westhoughton'}, {'lat': np.float64(51.3589), 'long': np.float64(1.4394), 'officialname': 'Broadstairs'</v>
-      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -2210,13 +2199,8 @@
         <f t="shared" si="0"/>
         <v>{'lat': np.float64(50.9025), 'long': np.float64(-1.4042), 'officialname': 'Southampton'}</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="L5" s="1" t="str">
-        <f>L4&amp;"]"</f>
-        <v>[{'lat': np.float64(51.5072), 'long': np.float64(-0.1275), 'officialname': 'London'}, {'lat': np.float64(52.48), 'long': np.float64(-1.9025), 'officialname': 'Birmingham'}, {'lat': np.float64(50.8058), 'long': np.float64(-1.0872), 'officialname': 'Portsmouth'}, {'lat': np.float64(50.9025), 'long': np.float64(-1.4042), 'officialname': 'Southampton'}, {'lat': np.float64(52.9561), 'long': np.float64(-1.1512), 'officialname': 'Nottingham'}, {'lat': np.float64(51.4536), 'long': np.float64(-2.5975), 'officialname': 'Bristol'}, {'lat': np.float64(53.479), 'long': np.float64(-2.2452), 'officialname': 'Manchester'}, {'lat': np.float64(53.4094), 'long': np.float64(-2.9785), 'officialname': 'Liverpool'}, {'lat': np.float64(52.6344), 'long': np.float64(-1.1319), 'officialname': 'Leicester'}, {'lat': np.float64(50.8147), 'long': np.float64(-0.3714), 'officialname': 'Worthing'}, {'lat': np.float64(52.4081), 'long': np.float64(-1.5106), 'officialname': 'Coventry'}, {'lat': np.float64(54.5964), 'long': np.float64(-5.93), 'officialname': 'Belfast'}, {'lat': np.float64(53.8), 'long': np.float64(-1.75), 'officialname': 'Bradford'}, {'lat': np.float64(52.9247), 'long': np.float64(-1.478), 'officialname': 'Derby'}, {'lat': np.float64(50.3714), 'long': np.float64(-4.1422), 'officialname': 'Plymouth'}, {'lat': np.float64(51.4947), 'long': np.float64(-0.1353), 'officialname': 'Westminster'}, {'lat': np.float64(52.5833), 'long': np.float64(-2.1333), 'officialname': 'Wolverhampton'}, {'lat': np.float64(52.2304), 'long': np.float64(-0.8938), 'officialname': 'Northampton'}, {'lat': np.float64(52.6286), 'long': np.float64(1.2928), 'officialname': 'Norwich'}, {'lat': np.float64(51.8783), 'long': np.float64(-0.4147), 'officialname': 'Luton'}, {'lat': np.float64(52.413), 'long': np.float64(-1.778), 'officialname': 'Solihull'}, {'lat': np.float64(51.544), 'long': np.float64(-0.1027), 'officialname': 'Islington'}, {'lat': np.float64(57.15), 'long': np.float64(-2.11), 'officialname': 'Aberdeen'}, {'lat': np.float64(51.3727), 'long': np.float64(-0.1099), 'officialname': 'Croydon'}, {'lat': np.float64(50.72), 'long': np.float64(-1.88), 'officialname': 'Bournemouth'}, {'lat': np.float64(51.58), 'long': np.float64(0.49), 'officialname': 'Basildon'}, {'lat': np.float64(51.272), 'long': np.float64(0.529), 'officialname': 'Maidstone'}, {'lat': np.float64(51.5575), 'long': np.float64(0.0858), 'officialname': 'Ilford'}, {'lat': np.float64(53.39), 'long': np.float64(-2.59), 'officialname': 'Warrington'}, {'lat': np.float64(51.75), 'long': np.float64(-1.25), 'officialname': 'Oxford'}, {'lat': np.float64(51.5836), 'long': np.float64(-0.3464), 'officialname': 'Harrow'}, {'lat': np.float64(52.519), 'long': np.float64(-1.995), 'officialname': 'West Bromwich'}, {'lat': np.float64(51.8667), 'long': np.float64(-2.25), 'officialname': 'Gloucester'}, {'lat': np.float64(53.96), 'long': np.float64(-1.08), 'officialname': 'York'}, {'lat': np.float64(53.8142), 'long': np.float64(-3.0503), 'officialname': 'Blackpool'}, {'lat': np.float64(53.4083), 'long': np.float64(-2.1494), 'officialname': 'Stockport'}, {'lat': np.float64(53.424), 'long': np.float64(-2.322), 'officialname': 'Sale'}, {'lat': np.float64(51.5975), 'long': np.float64(-0.0681), 'officialname': 'Tottenham'}, {'lat': np.float64(52.2053), 'long': np.float64(0.1192), 'officialname': 'Cambridge'}, {'lat': np.float64(51.5768), 'long': np.float64(0.1801), 'officialname': 'Romford'}, {'lat': np.float64(51.8917), 'long': np.float64(0.903), 'officialname': 'Colchester'}, {'lat': np.float64(51.6287), 'long': np.float64(-0.7482), 'officialname': 'High Wycombe'}, {'lat': np.float64(54.9556), 'long': np.float64(-1.6), 'officialname': 'Gateshead'}, {'lat': np.float64(51.5084), 'long': np.float64(-0.5881), 'officialname': 'Slough'}, {'lat': np.float64(53.748), 'long': np.float64(-2.482), 'officialname': 'Blackburn'}, {'lat': np.float64(51.73), 'long': np.float64(0.48), 'officialname': 'Chelmsford'}, {'lat': np.float64(53.61), 'long': np.float64(-2.16), 'officialname': 'Rochdale'}, {'lat': np.float64(53.43), 'long': np.float64(-1.357), 'officialname': 'Rotherham'}, {'lat': np.float64(51.584), 'long': np.float64(-0.021), 'officialname': 'Walthamstow'}, {'lat': np.float64(51.2667), 'long': np.float64(-1.0876), 'officialname': 'Basingstoke'}, {'lat': np.float64(53.483), 'long': np.float64(-2.2931), 'officialname': 'Salford'}, {'lat': np.float64(51.4668), 'long': np.float64(-0.375), 'officialname': 'Hounslow'}, {'lat': np.float64(51.5528), 'long': np.float64(-0.2979), 'officialname': 'Wembley'}, {'lat': np.float64(52.1911), 'long': np.float64(-2.2206), 'officialname': 'Worcester'}, {'lat': np.float64(51.4928), 'long': np.float64(-0.2229), 'officialname': 'Hammersmith'}, {'lat': np.float64(51.5864), 'long': np.float64(0.6049), 'officialname': 'Rayleigh'}, {'lat': np.float64(51.7526), 'long': np.float64(-0.4692), 'officialname': 'Hemel Hempstead'}, {'lat': np.float64(51.38), 'long': np.float64(-2.36), 'officialname': 'Bath'}, {'lat': np.float64(51.5127), 'long': np.float64(-0.4211), 'officialname': 'Hayes'}, {'lat': np.float64(54.527), 'long': np.float64(-1.5526), 'officialname': 'Darlington'}, {'lat': np.float64(50.8352), 'long': np.float64(-0.1758), 'officialname': 'Hove'}, {'lat': np.float64(50.85), 'long': np.float64(0.57), 'officialname': 'Hastings'}, {'lat': np.float64(51.655), 'long': np.float64(-0.3957), 'officialname': 'Watford'}, {'lat': np.float64(51.9017), 'long': np.float64(-0.2019), 'officialname': 'Stevenage'}, {'lat': np.float64(54.69), 'long': np.float64(-1.21), 'officialname': 'Hartlepool'}, {'lat': np.float64(53.19), 'long': np.float64(-2.89), 'officialname': 'Chester'}, {'lat': np.float64(51.4828), 'long': np.float64(-0.195), 'officialname': 'Fulham'}, {'lat': np.float64(52.523), 'long': np.float64(-1.468), 'officialname': 'Nuneaton'}, {'lat': np.float64(51.5175), 'long': np.float64(-0.2988), 'officialname': 'Ealing'}, {'lat': np.float64(51.8168), 'long': np.float64(-0.8124), 'officialname': 'Aylesbury'}, {'lat': np.float64(51.6154), 'long': np.float64(-0.0708), 'officialname': 'Edmonton'}, {'lat': np.float64(51.755), 'long': np.float64(-0.336), 'officialname': 'Saint Albans'}, {'lat': np.float64(53.789), 'long': np.float64(-2.248), 'officialname': 'Burnley'}, {'lat': np.float64(53.7167), 'long': np.float64(-1.6356), 'officialname': 'Batley'}, {'lat': np.float64(53.5809), 'long': np.float64(-0.6502), 'officialname': 'Scunthorpe'}, {'lat': np.float64(52.508), 'long': np.float64(-2.089), 'officialname': 'Dudley'}, {'lat': np.float64(51.4575), 'long': np.float64(-0.1175), 'officialname': 'Brixton'}, {'lat': np.float64(51.5111), 'long': np.float64(-0.3756), 'officialname': 'Southall'}, {'lat': np.float64(55.8456), 'long': np.float64(-4.4239), 'officialname': 'Paisley'}, {'lat': np.float64(51.37), 'long': np.float64(0.52), 'officialname': 'Chatham'}, {'lat': np.float64(51.5323), 'long': np.float64(0.0554), 'officialname': 'East Ham'}, {'lat': np.float64(51.346), 'long': np.float64(-2.977), 'officialname': 'Weston-super-Mare'}, {'lat': np.float64(54.8947), 'long': np.float64(-2.9364), 'officialname': 'Carlisle'}, {'lat': np.float64(54.995), 'long': np.float64(-1.43), 'officialname': 'South Shields'}, {'lat': np.float64(55.7644), 'long': np.float64(-4.1769), 'officialname': 'East Kilbride'}, {'lat': np.float64(52.8019), 'long': np.float64(-1.6367), 'officialname': 'Burton upon Trent'}, {'lat': np.float64(53.9919), 'long': np.float64(-1.5378), 'officialname': 'Harrogate'}, {'lat': np.float64(53.099), 'long': np.float64(-2.44), 'officialname': 'Crewe'}, {'lat': np.float64(52.48), 'long': np.float64(1.75), 'officialname': 'Lowestoft'}, {'lat': np.float64(52.37), 'long': np.float64(-1.26), 'officialname': 'Rugby'}, {'lat': np.float64(51.623), 'long': np.float64(0.009), 'officialname': 'Chingford'}, {'lat': np.float64(51.5404), 'long': np.float64(-0.4778), 'officialname': 'Uxbridge'}, {'lat': np.float64(52.58), 'long': np.float64(-1.98), 'officialname': 'Walsall'}, {'lat': np.float64(51.475), 'long': np.float64(0.33), 'officialname': 'Grays'}, {'lat': np.float64(51.3868), 'long': np.float64(-0.4133), 'officialname': 'Walton upon Thames'}, {'lat': np.float64(51.4002), 'long': np.float64(-0.1086), 'officialname': 'Thornton Heath'}, {'lat': np.float64(51.599), 'long': np.float64(-0.187), 'officialname': 'Finchley'}, {'lat': np.float64(51.5), 'long': np.float64(-0.19), 'officialname': 'Kensington'}, {'lat': np.float64(52.974), 'long': np.float64(-0.0214), 'officialname': 'Boston'}, {'lat': np.float64(50.4353), 'long': np.float64(-3.5625), 'officialname': 'Paignton'}, {'lat': np.float64(50.88), 'long': np.float64(-1.03), 'officialname': 'Waterlooville'}, {'lat': np.float64(53.875), 'long': np.float64(-1.706), 'officialname': 'Guiseley'}, {'lat': np.float64(51.5565), 'long': np.float64(0.2128), 'officialname': 'Hornchurch'}, {'lat': np.float64(51.4009), 'long': np.float64(-0.1517), 'officialname': 'Mitcham'}, {'lat': np.float64(51.4496), 'long': np.float64(-0.4089), 'officialname': 'Feltham'}, {'lat': np.float64(52.4575), 'long': np.float64(-2.1479), 'officialname': 'Stourbridge'}, {'lat': np.float64(51.375), 'long': np.float64(0.5), 'officialname': 'Rochester'}, {'lat': np.float64(53.691), 'long': np.float64(-1.633), 'officialname': 'Dewsbury'}, {'lat': np.float64(51.5135), 'long': np.float64(-0.2707), 'officialname': 'Acton'}, {'lat': np.float64(51.449), 'long': np.float64(-0.337), 'officialname': 'Twickenham'}, {'lat': np.float64(53.046), 'long': np.float64(-2.993), 'officialname': 'Wrecsam'}, {'lat': np.float64(53.279), 'long': np.float64(-2.897), 'officialname': 'Ellesmere Port'}, {'lat': np.float64(54.66), 'long': np.float64(-5.67), 'officialname': 'Bangor'}, {'lat': np.float64(51.019), 'long': np.float64(-3.1), 'officialname': 'Taunton'}, {'lat': np.float64(52.7725), 'long': np.float64(-1.2078), 'officialname': 'Loughborough'}, {'lat': np.float64(51.54), 'long': np.float64(0.08), 'officialname': 'Barking'}, {'lat': np.float64(51.6185), 'long': np.float64(-0.2729), 'officialname': 'Edgware'}, {'lat': np.float64(50.8094), 'long': np.float64(-0.5409), 'officialname': 'Littlehampton'}, {'lat': np.float64(51.576), 'long': np.float64(-0.433), 'officialname': 'Ruislip'}, {'lat': np.float64(51.4279), 'long': np.float64(-0.1235), 'officialname': 'Streatham'}, {'lat': np.float64(51.132), 'long': np.float64(0.263), 'officialname': 'Royal Tunbridge Wells'}, {'lat': np.float64(53.35), 'long': np.float64(-3.003), 'officialname': 'Bebington'}, {'lat': np.float64(53.25), 'long': np.float64(-2.13), 'officialname': 'Macclesfield'}, {'lat': np.float64(52.3028), 'long': np.float64(-0.6944), 'officialname': 'Wellingborough'}, {'lat': np.float64(52.3931), 'long': np.float64(-0.7229), 'officialname': 'Kettering'}, {'lat': np.float64(51.878), 'long': np.float64(0.55), 'officialname': 'Braintree'}, {'lat': np.float64(52.2919), 'long': np.float64(-1.5358), 'officialname': 'Royal Leamington Spa'}, {'lat': np.float64(54.1108), 'long': np.float64(-3.2261), 'officialname': 'Barrow in Furness'}, {'lat': np.float64(56.0719), 'long': np.float64(-3.4393), 'officialname': 'Dunfermline'}, {'lat': np.float64(53.3838), 'long': np.float64(-2.3547), 'officialname': 'Altrincham'}, {'lat': np.float64(54.0489), 'long': np.float64(-2.8014), 'officialname': 'Lancaster'}, {'lat': np.float64(53.4872), 'long': np.float64(-3.0343), 'officialname': 'Crosby'}, {'lat': np.float64(53.4457), 'long': np.float64(-2.9891), 'officialname': 'Bootle'}, {'lat': np.float64(51.5423), 'long': np.float64(-0.0026), 'officialname': 'Stratford'}, {'lat': np.float64(51.0792), 'long': np.float64(1.1794), 'officialname': 'Folkestone'}, {'lat': np.float64(55.945), 'long': np.float64(-3.994), 'officialname': 'Cumbernauld'}, {'lat': np.float64(51.208), 'long': np.float64(-1.48), 'officialname': 'Andover'}, {'lat': np.float64(51.66), 'long': np.float64(-3.81), 'officialname': 'Neath'}, {'lat': np.float64(52.488), 'long': np.float64(-2.05), 'officialname': 'Rowley Regis'}, {'lat': np.float64(54.2825), 'long': np.float64(-0.4), 'officialname': 'Scarborough'}, {'lat': np.float64(55.98), 'long': np.float64(-3.17), 'officialname': 'Leith'}, {'lat': np.float64(50.9452), 'long': np.float64(-2.637), 'officialname': 'Yeovil'}, {'lat': np.float64(51.451), 'long': np.float64(0.052), 'officialname': 'Eltham'}, {'lat': np.float64(51.5541), 'long': np.float64(-0.1744), 'officialname': 'Hampstead'}, {'lat': np.float64(53.125), 'long': np.float64(-1.261), 'officialname': 'Sutton in Ashfield'}, {'lat': np.float64(51.4015), 'long': np.float64(-0.1949), 'officialname': 'Morden'}, {'lat': np.float64(51.6444), 'long': np.float64(-0.1997), 'officialname': 'Barnet'}, {'lat': np.float64(53.4466), 'long': np.float64(-2.3086), 'officialname': 'Stretford'}, {'lat': np.float64(51.408), 'long': np.float64(-0.022), 'officialname': 'Beckenham'}, {'lat': np.float64(51.5299), 'long': np.float64(-0.3488), 'officialname': 'Greenford'}, {'lat': np.float64(51.702), 'long': np.float64(-0.035), 'officialname': 'Cheshunt'}, {'lat': np.float64(53.48), 'long': np.float64(-2.89), 'officialname': 'Kirkby'}, {'lat': np.float64(51.07), 'long': np.float64(-1.79), 'officialname': 'Salisbury'}, {'lat': np.float64(53.4897), 'long': np.float64(-2.0952), 'officialname': 'Ashton'}, {'lat': np.float64(51.394), 'long': np.float64(-0.307), 'officialname': 'Surbiton'}, {'lat': np.float64(53.716), 'long': np.float64(-1.356), 'officialname': 'Castleford'}, {'lat': np.float64(51.4452), 'long': np.float64(-0.0207), 'officialname': 'Catford'}, {'lat': np.float64(53.3042), 'long': np.float64(-1.1244), 'officialname': 'Worksop'}, {'lat': np.float64(53.7492), 'long': np.float64(-1.6023), 'officialname': 'Morley'}, {'lat': np.float64(51.743), 'long': np.float64(-3.378), 'officialname': 'Merthyr Tudful'}, {'lat': np.float64(53.555), 'long': np.float64(-2.187), 'officialname': 'Middleton'}, {'lat': np.float64(51.2834), 'long': np.float64(-0.8456), 'officialname': 'Fleet'}, {'lat': np.float64(50.85), 'long': np.float64(-1.18), 'officialname': 'Fareham'}, {'lat': np.float64(53.4487), 'long': np.float64(-2.3747), 'officialname': 'Urmston'}, {'lat': np.float64(51.3656), 'long': np.float64(-0.1963), 'officialname': 'Sutton'}, {'lat': np.float64(51.578), 'long': np.float64(-3.218), 'officialname': 'Caerphilly'}, {'lat': np.float64(51.128), 'long': np.float64(-2.993), 'officialname': 'Bridgwater'}, {'lat': np.float64(51.401), 'long': np.float64(-1.323), 'officialname': 'Newbury'}, {'lat': np.float64(51.4594), 'long': np.float64(0.1097), 'officialname': 'Welling'}, {'lat': np.float64(51.46), 'long': np.float64(-2.505), 'officialname': 'Kingswood'}, {'lat': np.float64(51.886), 'long': np.float64(-0.521), 'officialname': 'Dunstable'}, {'lat': np.float64(51.336), 'long': np.float64(1.416), 'officialname': 'Ramsgate'}, {'lat': np.float64(51.393), 'long': np.float64(0.478), 'officialname': 'Strood'}, {'lat': np.float64(53.5533), 'long': np.float64(-0.0215), 'officialname': 'Cleethorpes'}, {'lat': np.float64(51.5932), 'long': np.float64(-0.3894), 'officialname': 'Pinner'}, {'lat': np.float64(52.606), 'long': np.float64(1.729), 'officialname': 'Great Yarmouth'}, {'lat': np.float64(52.9711), 'long': np.float64(-1.3092), 'officialname': 'Ilkeston'}, {'lat': np.float64(53.653), 'long': np.float64(-2.632), 'officialname': 'Chorley'}, {'lat': np.float64(51.37), 'long': np.float64(1.13), 'officialname': 'Herne Bay'}, {'lat': np.float64(51.872), 'long': np.float64(0.1725), 'officialname': 'Bishops Stortford'}, {'lat': np.float64(53.005), 'long': np.float64(-1.127), 'officialname': 'Arnold'}, {'lat': np.float64(52.724), 'long': np.float64(-1.369), 'officialname': 'Coalville'}, {'lat': np.float64(51.994), 'long': np.float64(-0.732), 'officialname': 'Bletchley'}, {'lat': np.float64(51.9165), 'long': np.float64(-0.6617), 'officialname': 'Leighton Buzzard'}, {'lat': np.float64(55.86), 'long': np.float64(-3.98), 'officialname': 'Airdrie'}, {'lat': np.float64(55.126), 'long': np.float64(-1.514), 'officialname': 'Blyth'}, {'lat': np.float64(51.574), 'long': np.float64(0.4181), 'officialname': 'Laindon'}, {'lat': np.float64(51.684), 'long': np.float64(-4.163), 'officialname': 'Llanelli'}, {'lat': np.float64(52.927), 'long': np.float64(-1.215), 'officialname': 'Beeston'}, {'lat': np.float64(52.4629), 'long': np.float64(-1.8542), 'officialname': 'Small Heath'}, {'lat': np.float64(55.0456), 'long': np.float64(-1.4443), 'officialname': 'Whitley Bay'}, {'lat': np.float64(53.4554), 'long': np.float64(-2.1122), 'officialname': 'Denton'}, {'lat': np.float64(52.932), 'long': np.float64(-1.127), 'officialname': 'West Bridgford'}, {'lat': np.float64(51.6578), 'long': np.float64(-0.2722), 'officialname': 'Borehamwood'}, {'lat': np.float64(56.0011), 'long': np.float64(-3.7835), 'officialname': 'Falkirk'}, {'lat': np.float64(53.5239), 'long': np.float64(-2.3991), 'officialname': 'Walkden'}, {'lat': np.float64(51.5878), 'long': np.float64(-0.3086), 'officialname': 'Kenton'}, {'lat': np.float64(54.0819), 'long': np.float64(-0.1923), 'officialname': 'Bridlington'}, {'lat': np.float64(54.61), 'long': np.float64(-1.27), 'officialname': 'Billingham'}, {'lat': np.float64(52.918), 'long': np.float64(-0.638), 'officialname': 'Grantham'}, {'lat': np.float64(55.0097), 'long': np.float64(-1.4448), 'officialname': 'North Shields'}, {'lat': np.float64(51.947), 'long': np.float64(-0.283), 'officialname': 'Hitchin'}, {'lat': np.float64(52.7858), 'long': np.float64(-0.1529), 'officialname': 'Spalding'}, {'lat': np.float64(51.36), 'long': np.float64(0.61), 'officialname': 'Rainham'}, {'lat': np.float64(51.978), 'long': np.float64(-0.23), 'officialname': 'Letchworth'}, {'lat': np.float64(51.6114), 'long': np.float64(0.5207), 'officialname': 'Wickford'}, {'lat': np.float64(53.4111), 'long': np.float64(-2.8403), 'officialname': 'Huyton'}, {'lat': np.float64(51.6717), 'long': np.float64(-1.2783), 'officialname': 'Abingdon'}, {'lat': np.float64(51.32), 'long': np.float64(-2.208), 'officialname': 'Trowbridge'}, {'lat': np.float64(52.5812), 'long': np.float64(-1.093), 'officialname': 'Wigston Magna'}, {'lat': np.float64(51.606), 'long': np.float64(-1.241), 'officialname': 'Didcot'}, {'lat': np.float64(51.433), 'long': np.float64(-0.933), 'officialname': 'Earley'}, {'lat': np.float64(51.459), 'long': np.float64(0.138), 'officialname': 'Bexleyheath'}, {'lat': np.float64(53.4429), 'long': np.float64(-1.4698), 'officialname': 'Ecclesfield'}, {'lat': np.float64(53.698), 'long': np.float64(-2.461), 'officialname': 'Darwen'}, {'lat': np.float64(53.5333), 'long': np.float64(-2.2833), 'officialname': 'Prestwich'}, {'lat': np.float64(51.602), 'long': np.float64(-3.342), 'officialname': 'Pontypridd'}, {'lat': np.float64(55.828), 'long': np.float64(-4.214), 'officialname': 'Rutherglen'}, {'lat': np.float64(51.1295), 'long': np.float64(1.3089), 'officialname': 'Dover'}, {'lat': np.float64(50.8365), 'long': np.float64(-0.7792), 'officialname': 'Chichester'}, {'lat': np.float64(51.2226), 'long': np.float64(1.4006), 'officialname': 'Deal'}, {'lat': np.float64(51.9), 'long': np.float64(-1.15), 'officialname': 'Bicester'}, {'lat': np.float64(51.5467), 'long': np.float64(-0.37), 'officialname': 'Northolt'}, {'lat': np.float64(55.7742), 'long': np.float64(-3.9183), 'officialname': 'Wishaw'}, {'lat': np.float64(51.3652), 'long': np.float64(-0.1676), 'officialname': 'Carshalton'}, {'lat': np.float64(53.001), 'long': np.float64(-1.197), 'officialname': 'Bulwell'}, {'lat': np.float64(54.591), 'long': np.float64(-5.68), 'officialname': 'Newtownards'}, {'lat': np.float64(54.326), 'long': np.float64(-2.745), 'officialname': 'Kendal'}, {'lat': np.float64(55.082), 'long': np.float64(-1.585), 'officialname': 'Cramlington'}, {'lat': np.float64(52.3353), 'long': np.float64(-2.0579), 'officialname': 'Bromsgrove'}, {'lat': np.float64(51.703), 'long': np.float64(-3.041), 'officialname': 'Pont-y-p≈µl'}, {'lat': np.float64(51.509), 'long': np.float64(-0.338), 'officialname': 'Hanwell'}, {'lat': np.float64(51.2279), 'long': np.float64(-2.3215), 'officialname': 'Frome'}, {'lat': np.float64(51.5981), 'long': np.float64(-0.1149), 'officialname': 'Wood Green'}, {'lat': np.float64(52.5708), 'long': np.float64(-2.0457), 'officialname': 'Darlaston'}, {'lat': np.float64(55.181), 'long': np.float64(-1.568), 'officialname': 'Ashington'}, {'lat': np.float64(52.9877), 'long': np.float64(-2.1327), 'officialname': 'Longton'}, {'lat': np.float64(52.7661), 'long': np.float64(-0.886), 'officialname': 'Melton Mowbray'}, {'lat': np.float64(52.606), 'long': np.float64(-1.9179), 'officialname': 'Aldridge'}, {'lat': np.float64(53.5452), 'long': np.float64(-2.3999), 'officialname': 'Farnworth'}, {'lat': np.float64(51.552), 'long': np.float64(-0.097), 'officialname': 'Highbury'}, {'lat': np.float64(53.3761), 'long': np.float64(-2.1897), 'officialname': 'Cheadle Hulme'}, {'lat': np.float64(54.62), 'long': np.float64(-1.58), 'officialname': 'Newton Aycliffe'}, {'lat': np.float64(52.4299), 'long': np.float64(-1.9355), 'officialname': 'Bournville'}, {'lat': np.float64(52.009), 'long': np.float64(-0.789), 'officialname': 'Shenley Brook End'}, {'lat': np.float64(54.85), 'long': np.float64(-1.83), 'officialname': 'Consett'}, {'lat': np.float64(51.3211), 'long': np.float64(-0.1386), 'officialname': 'Coulsdon'}, {'lat': np.float64(52.566), 'long': np.float64(-2.0728), 'officialname': 'Bilston'}, {'lat': np.float64(52.7001), 'long': np.float64(-2.5157), 'officialname': 'Wellington'}, {'lat': np.float64(54.663), 'long': np.float64(-1.676), 'officialname': 'Bishop Auckland'}, {'lat': np.float64(52.395), 'long': np.float64(-1.979), 'officialname': 'Longbridge'}, {'lat': np.float64(52.614), 'long': np.float64(-2.004), 'officialname': 'Bloxwich'}, {'lat': np.float64(51.5557), 'long': np.float64(0.2512), 'officialname': 'Upminster'}, {'lat': np.float64(53.321), 'long': np.float64(-3.48), 'officialname': 'Rhyl'}, {'lat': np.float64(52.267), 'long': np.float64(-2.153), 'officialname': 'Droitwich'}, {'lat': np.float64(53.5355), 'long': np.float64(-2.5658), 'officialname': 'Hindley'}, {'lat': np.float64(53.549), 'long': np.float64(-2.529), 'officialname': 'Westhoughton'}, {'lat': np.float64(51.3589), 'long': np.float64(1.4394), 'officialname': 'Broadstairs']</v>
-      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
